--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>279271</t>
+          <t>137749</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76772</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS </t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REY </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,75 +613,71 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6561837211</t>
+          <t>6862339785</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FBDFG</t>
+          <t>STO. DOMINGO DE CUBA 352</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-06-1985</t>
+          <t>05-02-2009</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JUANCARLOSTOVARREY1985@GMAIL.COM</t>
+          <t>HAZZIEL5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>17-02-2025 18:22:50</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>07-12-2022 05:23:48</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:20</t>
+          <t>02-02-2026 20:32:51</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>08-02-2026 15:26:21</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,18 +685,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26010522202230003395</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26020522023180001171</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>137749</t>
+          <t>187923</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>85430</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">JOVANI </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">RIOS </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +744,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6862339785</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>STO. DOMINGO DE CUBA 352</t>
-        </is>
-      </c>
+          <t>6864631541</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>05-02-2009</t>
+          <t>08-05-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HAZZIEL5@HOTMAIL.COM</t>
+          <t>JOVANIRIOS123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>07-12-2022 05:23:48</t>
+          <t>31-07-2023 18:30:37</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -802,18 +790,18 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-02-2026 20:32:51</t>
+          <t>16-02-2026 14:10:53</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -824,7 +812,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26020522023180001171</t>
+          <t>26030522389830002053</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -848,12 +836,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>187923</t>
+          <t>309811</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>85430</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOVANI </t>
+          <t xml:space="preserve">TRINIDAD </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIOS </t>
+          <t xml:space="preserve">CONTRERAS </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,67 +871,75 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6864631541</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6861515159</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CALLE CONDOR</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08-05-2005</t>
+          <t>02-08-1959</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JOVANIRIOS123@GMAIL.COM</t>
+          <t>TRINIDADCONTRERAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31-07-2023 18:30:37</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>18-08-2025 08:33:22</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE JUBILADOS $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:53</t>
+          <t>18-02-2026 08:22:35</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>18-02-2026 08:21:16</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -951,36 +947,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522389830002053</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26020522457020001079</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>309811</t>
+          <t>323166</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRINIDAD </t>
+          <t xml:space="preserve">HILARIO </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>SORIA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,75 +1014,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6861515159</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CALLE CONDOR</t>
-        </is>
-      </c>
+          <t>6461851555</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-08-1959</t>
+          <t>03-11-1954</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TRINIDADCONTRERAS@GMAIL.COM</t>
+          <t>HSORIA777@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>18-08-2025 08:33:22</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>11-11-2025 15:37:08</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE JUBILADOS $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>18-02-2026 08:22:35</t>
+          <t>16-02-2026 20:10:42</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>18-02-2026 08:21:16</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,44 +1082,40 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522457020001079</t>
+          <t>26030522409980002085</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>323166</t>
+          <t>328372</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HILARIO </t>
+          <t xml:space="preserve">LETICIA ISABEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SORIA</t>
+          <t xml:space="preserve">VALENCIA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">MUNGUIA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,67 +1145,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461851555</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6861009814</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SANTA LUCIA</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03-11-1954</t>
+          <t>13-08-1974</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HSORIA777@HOTMAIL.COM</t>
+          <t>ISABELMUNGUIA._13@OULOCK.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11-11-2025 15:37:08</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-12-2025 13:53:42</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>16-02-2026 20:10:42</t>
+          <t>12-02-2026 20:34:35</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12-02-2026 20:33:56</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,18 +1221,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522409980002085</t>
+          <t>26030522306250001944</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>CONSUELO ELOISA OLIVARES SALAS</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1249,12 +1253,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>328372</t>
+          <t>144848</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LETICIA ISABEL </t>
+          <t xml:space="preserve">SARAHI </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENCIA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNGUIA </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,12 +1288,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6861009814</t>
+          <t>6863396414</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SANTA LUCIA</t>
+          <t>CALLE MISON CERRADA 261</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,60 +1303,56 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-08-1974</t>
+          <t>27-02-1995</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ISABELMUNGUIA._13@OULOCK.COM</t>
+          <t>27.SARAHI.LOPEZG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10-12-2025 13:53:42</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>16-01-2023 07:46:29</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12-02-2026 20:34:35</t>
+          <t>11-02-2026 21:39:51</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>12-02-2026 20:33:56</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1360,22 +1360,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030522306250001944</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>CONSUELO ELOISA OLIVARES SALAS</t>
-        </is>
-      </c>
+          <t>26030522279520001912</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1392,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>144848</t>
+          <t>158452</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1407,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI </t>
+          <t xml:space="preserve">LAURA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">BRIST </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BRIST</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1427,32 +1419,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863396414</t>
+          <t>6861199601</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CALLE MISON CERRADA 261</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27-02-1995</t>
+          <t>30-01-1978</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27.SARAHI.LOPEZG@GMAIL.COM</t>
+          <t>LAU.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16-01-2023 07:46:29</t>
+          <t>14-03-2023 16:35:02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1477,18 +1469,18 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>11-02-2026 21:39:51</t>
+          <t>14-02-2026 09:36:04</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1499,7 +1491,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26030522279520001912</t>
+          <t>26030522344870002003</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1511,24 +1503,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>158452</t>
+          <t>195748</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>93255</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAURA </t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIST </t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BRIST</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,71 +1550,75 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6861199601</t>
+          <t>6862659517</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>SEDF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-01-1978</t>
+          <t>26-06-1991</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LAU.@GMAIL.COM</t>
+          <t>ANITA_JACK8@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14-03-2023 16:35:02</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-09-2023 18:05:29</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:36:04</t>
+          <t>02-02-2026 17:06:44</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:06:14</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1630,14 +1626,22 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26030522344870002003</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26010522017990002763</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1654,12 +1658,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>195748</t>
+          <t>231010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t xml:space="preserve">ALBERTO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APARICIO</t>
+          <t xml:space="preserve">BLANCO </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t xml:space="preserve">CEBREROS </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,75 +1693,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6862659517</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SEDF</t>
-        </is>
-      </c>
+          <t>6865975644</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-06-1991</t>
+          <t>16-01-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ANITA_JACK8@HOTMAIL.COM</t>
+          <t>ABLANCEBR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>08-09-2023 18:05:29</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>23-04-2024 14:07:17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 17:06:44</t>
+          <t>03-02-2026 14:18:41</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:06:14</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1765,44 +1761,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26010522017990002763</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26030522040950001456</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>231010</t>
+          <t>334762</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1800,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t xml:space="preserve">JUANA MAGDALENA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCO </t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CEBREROS </t>
+          <t>GALVEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,10 +1820,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6865975644</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6862268524</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PARAJES DE PUEBLA</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1843,56 +1835,60 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>16-01-2005</t>
+          <t>24-06-1973</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ABLANCEBR@GMAIL.COM</t>
+          <t>LUNAMALENA2473@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>23-04-2024 14:07:17</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-01-2026 16:14:31</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-02-2026 14:18:41</t>
+          <t>05-02-2026 15:08:35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>05-02-2026 15:07:47</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1900,19 +1896,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26030522040950001456</t>
+          <t>26030522107950001586</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1924,12 +1920,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>334762</t>
+          <t>330935</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1935,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA MAGDALENA </t>
+          <t>MARCO RAMSES</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>URQUIJO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GALVEZ</t>
+          <t>UREÑA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,14 +1955,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862268524</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PARAJES DE PUEBLA</t>
-        </is>
-      </c>
+          <t>6862239164</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1974,60 +1966,56 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24-06-1973</t>
+          <t>02-10-2003</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LUNAMALENA2473@GMAIL.COM</t>
+          <t>MURQUIJOURENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14-01-2026 16:14:31</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>29-12-2025 17:42:21</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-02-2026 15:08:35</t>
+          <t>02-02-2026 18:48:58</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>05-02-2026 15:07:47</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2035,36 +2023,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26030522107950001586</t>
+          <t>26030522021130001423</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Eduardo  Rivera Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>330935</t>
+          <t>339905</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2062,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARCO RAMSES</t>
+          <t xml:space="preserve">ABRIL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>URQUIJO</t>
+          <t xml:space="preserve">ESTRADA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UREÑA</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,28 +2082,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862239164</t>
+          <t>6951109611</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02-10-2003</t>
+          <t>08-04-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MURQUIJOURENA@GMAIL.COM</t>
+          <t>ABRIL_OLIVARES98@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29-12-2025 17:42:21</t>
+          <t>02-02-2026 08:25:17</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2130,22 +2118,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 18:48:58</t>
+          <t>02-02-2026 08:27:19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2162,24 +2150,24 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26030522021130001423</t>
+          <t>26030522001120001377</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2305,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339905</t>
+          <t>340851</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2332,17 +2320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABRIL </t>
+          <t xml:space="preserve">ALBA CRISTINA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTRADA </t>
+          <t xml:space="preserve">ALMODOVAR </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2352,10 +2340,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6951109611</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6862238374</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CERADA CICA 4193</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2363,56 +2355,60 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08-04-1998</t>
+          <t>18-06-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ABRIL_OLIVARES98@HOTMAIL.COM</t>
+          <t>ALMODOVARALBA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 08:25:17</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 05:14:54</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 08:27:19</t>
+          <t>04-02-2026 05:21:38</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-02-2026 05:20:34</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2420,14 +2416,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26030522001120001377</t>
+          <t>26030522065870001511</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2579,12 +2575,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>341163</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2590,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBA CRISTINA </t>
+          <t>ANGELICA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMODOVAR </t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,12 +2610,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862238374</t>
+          <t>6861724482</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CERADA CICA 4193</t>
+          <t>VALLE DORADO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2629,17 +2625,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-06-1992</t>
+          <t>05-03-1989</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ALMODOVARALBA06@GMAIL.COM</t>
+          <t>VANE_ANGY@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 05:14:54</t>
+          <t>04-02-2026 19:12:33</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2660,7 +2656,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 05:21:38</t>
+          <t>04-02-2026 19:20:15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2670,7 +2666,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>04-02-2026 05:20:34</t>
+          <t>04-02-2026 19:18:02</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2690,7 +2686,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26030522065870001511</t>
+          <t>26030522087770001545</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2702,7 +2698,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2714,12 +2710,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340856</t>
+          <t>279271</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>76772</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2729,17 +2725,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE </t>
+          <t xml:space="preserve">JUAN CARLOS </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVELAR </t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTEZ </t>
+          <t xml:space="preserve">REY </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2749,12 +2745,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861774394</t>
+          <t>6561837211</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RIO GARONA 3425</t>
+          <t>FBDFG</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2764,17 +2760,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>22-07-1978</t>
+          <t>22-06-1985</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ENRIQUE.AVELAR@GULFSTREAM.COM</t>
+          <t>JUANCARLOSTOVARREY1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 05:30:05</t>
+          <t>17-02-2025 18:22:50</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2795,17 +2791,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 05:32:15</t>
+          <t>09-02-2026 17:27:20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-02-2026 05:31:49</t>
+          <t>08-02-2026 15:26:21</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2825,10 +2821,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26030522066150001513</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26010522202230003395</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2837,24 +2837,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340398</t>
+          <t>310112</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KATHERINE</t>
+          <t xml:space="preserve">RAYMUNDO </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2884,28 +2884,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6861938138</t>
+          <t>6861447809</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-01-2008</t>
+          <t>29-12-1967</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RODRIGUEZGARCIAKA@GMAIL.COM</t>
+          <t>RAYMUNDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 21:14:06</t>
+          <t>19-08-2025 09:08:36</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 21:16:38</t>
+          <t>18-02-2026 08:27:18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2952,11 +2952,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26030522023670001432</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26020522457140001080</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -2976,12 +2984,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340524</t>
+          <t>341340</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2991,17 +2999,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>IRMA PATRICIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3011,67 +3019,75 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6864295376</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6861615665</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NUEVO MEXICALI</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-12-2000</t>
+          <t>27-10-1970</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IVANVELARDE1213@GMAIL.COM</t>
+          <t>PATTY.MALDONADO.PINA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-02-2026 11:34:05</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 15:16:07</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-02-2026 11:35:27</t>
+          <t>09-02-2026 15:25:50</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>09-02-2026 15:25:26</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3079,14 +3095,18 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26030522037230001450</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26030522195390001733</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3103,12 +3123,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>340856</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3118,17 +3138,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ANGELICA</t>
+          <t xml:space="preserve">ENRIQUE </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t xml:space="preserve">AVELAR </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">CORTEZ </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3138,32 +3158,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861724482</t>
+          <t>6861774394</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VALLE DORADO</t>
+          <t>RIO GARONA 3425</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>05-03-1989</t>
+          <t>22-07-1978</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>VANE_ANGY@HOTMAIL.COM</t>
+          <t>ENRIQUE.AVELAR@GULFSTREAM.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:12:33</t>
+          <t>04-02-2026 05:30:05</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3184,7 +3204,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:20:15</t>
+          <t>04-02-2026 05:32:15</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3194,7 +3214,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-02-2026 19:18:02</t>
+          <t>04-02-2026 05:31:49</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3214,7 +3234,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26030522087770001545</t>
+          <t>26030522066150001513</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3226,24 +3246,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>310112</t>
+          <t>340398</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3253,19 +3273,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAYMUNDO </t>
+          <t>KATHERINE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JIMENEZ</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>52</t>
@@ -3273,28 +3293,28 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861447809</t>
+          <t>6861938138</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29-12-1967</t>
+          <t>30-01-2008</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>RAYMUNDOGARCIA@GMAIL.COM</t>
+          <t>RODRIGUEZGARCIAKA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19-08-2025 09:08:36</t>
+          <t>02-02-2026 21:14:06</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3319,12 +3339,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>18-02-2026 08:27:18</t>
+          <t>02-02-2026 21:16:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3341,19 +3361,11 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522457140001080</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>26030522023670001432</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>549</t>
@@ -3373,12 +3385,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>323154</t>
+          <t>340524</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3388,27 +3400,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GILDARDO</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RANGEL</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7602220877</t>
+          <t>6864295376</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3419,17 +3431,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-01-2004</t>
+          <t>13-12-2000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>GILDARDODGUEZ@GMAIL.COM</t>
+          <t>IVANVELARDE1213@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>11-11-2025 14:48:43</t>
+          <t>03-02-2026 11:34:05</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3444,28 +3456,28 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>19-02-2026 13:34:33</t>
+          <t>03-02-2026 11:35:27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3476,36 +3488,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26030522494230002262</t>
+          <t>26030522037230001450</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341340</t>
+          <t>342195</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3515,17 +3527,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IRMA PATRICIA</t>
+          <t>DIANA SOLEDAD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t xml:space="preserve">FONTES </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3535,12 +3547,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861615665</t>
+          <t>6862253619</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NUEVO MEXICALI</t>
+          <t>INDEPENDECIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3550,17 +3562,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27-10-1970</t>
+          <t>03-05-1987</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PATTY.MALDONADO.PINA@GMAIL.COM</t>
+          <t>DIANAFONTES0587@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-02-2026 15:16:07</t>
+          <t>09-02-2026 14:54:09</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3581,7 +3593,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 15:25:50</t>
+          <t>09-02-2026 14:57:19</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3591,7 +3603,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-02-2026 15:25:26</t>
+          <t>09-02-2026 14:56:47</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3601,7 +3613,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3611,14 +3623,10 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26030522195390001733</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522194160001730</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3627,7 +3635,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3639,12 +3647,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>339193</t>
+          <t>341326</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3654,17 +3662,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MAYRIM LIZBETH</t>
+          <t>DARIEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3674,28 +3682,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6863515972</t>
+          <t>6863548040</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-04-2006</t>
+          <t>01-09-2005</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OLIVARESMAYRIM3@GMAIL.COM</t>
+          <t>ELDARIELMARIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29-01-2026 20:17:57</t>
+          <t>05-02-2026 14:41:34</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3720,18 +3728,18 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-02-2026 21:06:32</t>
+          <t>10-02-2026 14:24:56</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3742,19 +3750,15 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26030522058680001505</t>
+          <t>26030522232430001810</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3762,24 +3766,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>317689</t>
+          <t>341448</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3789,17 +3793,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIANA YAZMIN</t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3809,10 +3813,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6863225684</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6863504849</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PUERTA</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3820,56 +3828,60 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-09-2004</t>
+          <t>02-11-1993</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>COTAVERADIANAYAZMIN.1D@GMAIL.COM</t>
+          <t>ANAKARENVZP@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>07-10-2025 14:08:20</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 20:07:27</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>16-02-2026 12:59:52</t>
+          <t>05-02-2026 20:25:49</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>05-02-2026 20:25:26</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3877,40 +3889,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26030522387820002050</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522119830001622</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342066</t>
+          <t>317689</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3920,17 +3928,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVANNA </t>
+          <t>DIANA YAZMIN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILERA </t>
+          <t>VERA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3940,14 +3948,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863403996</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AV. VALLE DE JUAREZ 2024</t>
-        </is>
-      </c>
+          <t>6863225684</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3955,60 +3959,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>06-08-2007</t>
+          <t>03-09-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>IVANNALIZ07@GMAIL.COM</t>
+          <t>COTAVERADIANAYAZMIN.1D@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 09:08:29</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>07-10-2025 14:08:20</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>11-02-2026 08:53:21</t>
+          <t>16-02-2026 12:59:52</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:52:44</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4016,27 +4016,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26030522260160001868</t>
+          <t>26030522387820002050</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>CONSUELO ELOISA OLIVARES SALAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4048,12 +4044,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341441</t>
+          <t>323154</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4063,27 +4059,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CARLOS AGUSTIN</t>
+          <t>GILDARDO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>RANGEL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861409324</t>
+          <t>7602220877</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4094,17 +4090,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>14-01-2004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CARLOSAGUSTIN.MENDEZ@UABC.EDU.MX</t>
+          <t>GILDARDODGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>05-02-2026 19:35:46</t>
+          <t>11-11-2025 14:48:43</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4119,28 +4115,28 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 19:14:03</t>
+          <t>19-02-2026 13:34:33</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -4151,40 +4147,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26030522246130001835</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522494230002262</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341326</t>
+          <t>342066</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4194,17 +4186,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DARIEL</t>
+          <t xml:space="preserve">IVANNA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">AGUILERA </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4214,67 +4206,75 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6863548040</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6863403996</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AV. VALLE DE JUAREZ 2024</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01-09-2005</t>
+          <t>06-08-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ELDARIELMARIO@GMAIL.COM</t>
+          <t>IVANNALIZ07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>05-02-2026 14:41:34</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 09:08:29</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 14:24:56</t>
+          <t>11-02-2026 08:53:21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:52:44</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4282,23 +4282,27 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26030522232430001810</t>
+          <t>26030522260160001868</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>CONSUELO ELOISA OLIVARES SALAS</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4310,12 +4314,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>341448</t>
+          <t>341441</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4325,17 +4329,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t>CARLOS AGUSTIN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4345,75 +4349,67 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863504849</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>PUERTA</t>
-        </is>
-      </c>
+          <t>6861409324</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-11-1993</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ANAKARENVZP@HOTMAIL.COM</t>
+          <t>CARLOSAGUSTIN.MENDEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>05-02-2026 20:07:27</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>05-02-2026 19:35:46</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>05-02-2026 20:25:49</t>
+          <t>10-02-2026 19:14:03</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>05-02-2026 20:25:26</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4421,36 +4417,40 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26030522119830001622</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+          <t>26030522246130001835</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342195</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIANA SOLEDAD</t>
+          <t xml:space="preserve">MARCELINA </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONTES </t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6862253619</t>
+          <t>6634048799</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INDEPENDECIA</t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4495,17 +4495,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03-05-1987</t>
+          <t>09-02-1990</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DIANAFONTES0587@GMAIL.COM</t>
+          <t>MYAM-18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 14:54:09</t>
+          <t>09-02-2026 18:32:21</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4526,17 +4526,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 14:57:19</t>
+          <t>11-02-2026 19:01:18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>09-02-2026 14:56:47</t>
+          <t>11-02-2026 19:00:38</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4556,11 +4556,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26030522194160001730</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26110522275680003096</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>DIARA IVETH HERNANDEZ RADILLA</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>499</t>
@@ -4568,24 +4576,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>339193</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4595,17 +4603,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>MAYRIM LIZBETH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4615,75 +4623,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861708535</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>GONZALEZ ORTEGA</t>
-        </is>
-      </c>
+          <t>6863515972</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16-07-1988</t>
+          <t>03-04-2006</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CHINOMXL@HOTMAIL.COM</t>
+          <t>OLIVARESMAYRIM3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-02-2026 17:27:41</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>29-01-2026 20:17:57</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 17:31:14</t>
+          <t>03-02-2026 21:06:32</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:30:51</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4691,36 +4691,44 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26030522018810001418</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26030522058680001505</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342396</t>
+          <t>342220</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,17 +4738,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCELINA </t>
+          <t>VENEZIA MILDRETH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4750,12 +4758,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6634048799</t>
+          <t>6863374140</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SANCHEZ TABOADA</t>
+          <t>PUERT DEL SOL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4765,17 +4773,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>09-02-1990</t>
+          <t>15-01-2007</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MYAM-18@GMAIL.COM</t>
+          <t>VENEZIACORRAL9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:21</t>
+          <t>09-02-2026 15:45:41</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4786,7 +4794,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4796,17 +4804,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>11-02-2026 19:01:18</t>
+          <t>09-02-2026 15:48:29</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11-02-2026 19:00:38</t>
+          <t>09-02-2026 15:47:18</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4826,19 +4834,11 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26110522275680003096</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>DIARA IVETH HERNANDEZ RADILLA</t>
-        </is>
-      </c>
+          <t>26030522196150001735</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4846,24 +4846,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342220</t>
+          <t>342515</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4873,17 +4873,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VENEZIA MILDRETH</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4893,32 +4893,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6863374140</t>
+          <t>6861587461</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PUERT DEL SOL</t>
+          <t xml:space="preserve">JOAQUIN AMARO </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15-01-2007</t>
+          <t>22-12-1987</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>VENEZIACORRAL9@GMAIL.COM</t>
+          <t>ZORDI.EDUARDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 15:45:41</t>
+          <t>10-02-2026 05:37:41</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4939,17 +4939,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 15:48:29</t>
+          <t>10-02-2026 05:40:22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-02-2026 15:47:18</t>
+          <t>10-02-2026 05:39:54</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26030522196150001735</t>
+          <t>26030522222310001786</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4981,24 +4981,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340719</t>
+          <t>342507</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5008,17 +5008,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t xml:space="preserve">CYNTHIA </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t xml:space="preserve">PIÑA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LLANES</t>
+          <t>TERAN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5028,32 +5028,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6865254236</t>
+          <t>6461790091</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AV. RANCHO GRANDE 1937</t>
+          <t>MAR BALTICO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12-08-1993</t>
+          <t>09-12-1976</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LUISESOTO258@GMAIL.COM</t>
+          <t>CINTHYATERAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:17:43</t>
+          <t>09-02-2026 22:00:59</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:20:41</t>
+          <t>10-02-2026 09:11:58</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:56</t>
+          <t>10-02-2026 09:10:45</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26030522048910001474</t>
+          <t>26080522226680002378</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5116,24 +5116,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342515</t>
+          <t>342540</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5143,17 +5143,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>OSCAR FERNANDO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6861587461</t>
+          <t>6863662750</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOAQUIN AMARO </t>
+          <t>AV. SAN PABLO 1656</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22-12-1987</t>
+          <t>21-11-2000</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ZORDI.EDUARDO@GMAIL.COM</t>
+          <t>RAMIREZ2167@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 05:37:41</t>
+          <t>10-02-2026 07:56:37</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 05:40:22</t>
+          <t>10-02-2026 08:01:48</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>10-02-2026 05:39:54</t>
+          <t>10-02-2026 08:01:02</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26030522222310001786</t>
+          <t>26030522224890001794</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340853</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUVIA </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5433,32 +5433,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6861523739</t>
+          <t>6861708535</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COLONIA MEZQUITAL 4232</t>
+          <t>GONZALEZ ORTEGA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>08-02-1988</t>
+          <t>16-07-1988</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>NUVIAVA742@GMAIL.COM</t>
+          <t>CHINOMXL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>04-02-2026 05:23:13</t>
+          <t>02-02-2026 17:27:41</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5479,17 +5479,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>04-02-2026 05:26:37</t>
+          <t>02-02-2026 17:31:14</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>04-02-2026 05:26:10</t>
+          <t>02-02-2026 17:30:51</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26030522065980001512</t>
+          <t>26030522018810001418</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5533,12 +5533,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343491</t>
+          <t>343853</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZELL  </t>
+          <t>KARLA LISSETE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONDACA </t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863457622</t>
+          <t>4491780397</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>POBLADO INDIVISO</t>
+          <t>TARCENTO #217</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25-10-2005</t>
+          <t>26-08-1996</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ITZELLMONDACA1027@GMAIL.COM</t>
+          <t>LISS.2484@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13-02-2026 13:16:20</t>
+          <t>15-02-2026 13:27:15</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5614,17 +5614,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>13-02-2026 13:20:14</t>
+          <t>15-02-2026 13:50:40</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13-02-2026 13:19:37</t>
+          <t>15-02-2026 13:49:20</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26030522320340001971</t>
+          <t>26190522367020003919</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5656,24 +5656,24 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343492</t>
+          <t>340853</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA DENISSE </t>
+          <t xml:space="preserve">NUVIA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6862768858</t>
+          <t>6861523739</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">EJIDO GUERRERO </t>
+          <t>COLONIA MEZQUITAL 4232</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5718,17 +5718,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>28-09-1998</t>
+          <t>08-02-1988</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DENISSE.TD@GMAIL.COM</t>
+          <t>NUVIAVA742@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13-02-2026 13:21:47</t>
+          <t>04-02-2026 05:23:13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5749,17 +5749,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>13-02-2026 13:25:14</t>
+          <t>04-02-2026 05:26:37</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>13-02-2026 13:24:52</t>
+          <t>04-02-2026 05:26:10</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26030522320400001972</t>
+          <t>26030522065980001512</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5791,24 +5791,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342507</t>
+          <t>341094</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYNTHIA </t>
+          <t>JAKELYN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PIÑA </t>
+          <t>PEREDA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TERAN</t>
+          <t>LIZAOLA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5838,14 +5838,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6461790091</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>MAR BALTICO</t>
-        </is>
-      </c>
+          <t>6861494317</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5853,60 +5849,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>09-12-1976</t>
+          <t>09-04-2010</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CINTHYATERAN@GMAIL.COM</t>
+          <t>PJAKELYN67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 22:00:59</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>04-02-2026 17:06:54</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-02-2026 09:11:58</t>
+          <t>04-02-2026 17:08:03</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>10-02-2026 09:10:45</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5914,36 +5906,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26080522226680002378</t>
+          <t>26030522081420001541</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342540</t>
+          <t>342947</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5953,17 +5945,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OSCAR FERNANDO</t>
+          <t>ROSALBA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>BOJORQUEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5973,32 +5965,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6863662750</t>
+          <t>6863931287</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AV. SAN PABLO 1656</t>
+          <t>RIO MEZCALAPA  Y OCTAVA 2941</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-11-2000</t>
+          <t>24-08-1976</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>RAMIREZ2167@HOTMAIL.COM</t>
+          <t>HERNANDEZBOJORQUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10-02-2026 07:56:37</t>
+          <t>11-02-2026 11:45:04</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6019,17 +6011,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>10-02-2026 08:01:48</t>
+          <t>11-02-2026 11:54:16</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>10-02-2026 08:01:02</t>
+          <t>11-02-2026 11:52:48</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6049,7 +6041,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26030522224890001794</t>
+          <t>26030522262490001876</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6061,24 +6053,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342511</t>
+          <t>343008</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6088,17 +6080,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIME ARTURO </t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>AGUILERA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVERA </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6108,12 +6100,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6861179222</t>
+          <t>6421499467</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIO CONGO </t>
+          <t>VALLE DE PEDREGAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6123,52 +6115,48 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27-03-1985</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JAIME.GARCIARIVERA@HOTMAIL.COM</t>
+          <t>ERICKAGUILERAMENDOZA14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 05:25:26</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 15:19:20</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 05:29:34</t>
+          <t>11-02-2026 15:24:43</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>10-02-2026 05:28:54</t>
+          <t>11-02-2026 15:23:47</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6178,7 +6166,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6188,19 +6176,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26030522222120001785</t>
+          <t>26030522266380001884</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6212,12 +6200,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>341440</t>
+          <t>340474</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6227,17 +6215,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>REGINA</t>
+          <t>SAHID</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MÉNDEZ</t>
+          <t>OLEA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LÓPEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6247,28 +6235,28 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6862143110</t>
+          <t>6861851195</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>08-09-2009</t>
+          <t>12-08-2005</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>MENDEZREGINA008@GMAIL.COM</t>
+          <t>SAHIDOLEADIAZ120805@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>05-02-2026 19:35:29</t>
+          <t>03-02-2026 08:37:15</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6293,12 +6281,12 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:47</t>
+          <t>03-02-2026 08:39:25</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -6315,19 +6303,11 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26030522246320001836</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>26030522034030001438</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>549</t>
@@ -6335,7 +6315,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6347,12 +6327,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>340474</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6362,17 +6342,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAHID</t>
+          <t xml:space="preserve">JAIME ARTURO </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OLEA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6382,10 +6362,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861851195</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6861179222</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO CONGO </t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6393,17 +6377,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12-08-2005</t>
+          <t>27-03-1985</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SAHIDOLEADIAZ120805@GMAIL.COM</t>
+          <t>JAIME.GARCIARIVERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>03-02-2026 08:37:15</t>
+          <t>10-02-2026 05:25:26</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6413,36 +6397,44 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>03-02-2026 08:39:25</t>
+          <t>10-02-2026 05:29:34</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:28:54</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6450,14 +6442,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26030522034030001438</t>
+          <t>26030522222120001785</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6474,12 +6466,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>341094</t>
+          <t>343491</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6489,17 +6481,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JAKELYN</t>
+          <t xml:space="preserve">ITZELL  </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PEREDA</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LIZAOLA</t>
+          <t xml:space="preserve">MONDACA </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6509,10 +6501,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861494317</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6863457622</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>POBLADO INDIVISO</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6520,56 +6516,60 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>09-04-2010</t>
+          <t>25-10-2005</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PJAKELYN67@GMAIL.COM</t>
+          <t>ITZELLMONDACA1027@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>04-02-2026 17:06:54</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 13:16:20</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>04-02-2026 17:08:03</t>
+          <t>13-02-2026 13:20:14</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>13-02-2026 13:19:37</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6577,19 +6577,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26030522081420001541</t>
+          <t>26030522320340001971</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6601,12 +6601,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342947</t>
+          <t>343492</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ROSALBA</t>
+          <t xml:space="preserve">PAULA DENISSE </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BOJORQUEZ</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6863931287</t>
+          <t>6862768858</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RIO MEZCALAPA  Y OCTAVA 2941</t>
+          <t xml:space="preserve">EJIDO GUERRERO </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24-08-1976</t>
+          <t>28-09-1998</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>HERNANDEZBOJORQUE@GMAIL.COM</t>
+          <t>DENISSE.TD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11-02-2026 11:45:04</t>
+          <t>13-02-2026 13:21:47</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6682,17 +6682,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>11-02-2026 11:54:16</t>
+          <t>13-02-2026 13:25:14</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11-02-2026 11:52:48</t>
+          <t>13-02-2026 13:24:52</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26030522262490001876</t>
+          <t>26030522320400001972</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6736,12 +6736,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343008</t>
+          <t>343372</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t xml:space="preserve">ANGEL DANIEL </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AGUILERA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6421499467</t>
+          <t>8446722943</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VALLE DE PEDREGAL</t>
+          <t>JUAN VERLANGA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>12-02-1990</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ERICKAGUILERAMENDOZA14@GMAIL.COM</t>
+          <t>ANGELGOOMEZ6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>11-02-2026 15:19:20</t>
+          <t>12-02-2026 18:39:44</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>11-02-2026 15:24:43</t>
+          <t>13-02-2026 17:04:43</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>11-02-2026 15:23:47</t>
+          <t>13-02-2026 17:03:35</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26030522266380001884</t>
+          <t>26190522325570003826</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6859,24 +6859,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343372</t>
+          <t>340719</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6886,17 +6886,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL DANIEL </t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LLANES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8446722943</t>
+          <t>6865254236</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JUAN VERLANGA</t>
+          <t>AV. RANCHO GRANDE 1937</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6921,17 +6921,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12-02-1990</t>
+          <t>12-08-1993</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ANGELGOOMEZ6@GMAIL.COM</t>
+          <t>LUISESOTO258@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>12-02-2026 18:39:44</t>
+          <t>03-02-2026 17:17:43</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6952,17 +6952,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>13-02-2026 17:04:43</t>
+          <t>03-02-2026 17:20:41</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:35</t>
+          <t>03-02-2026 17:19:56</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26190522325570003826</t>
+          <t>26030522048910001474</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343853</t>
+          <t>344799</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KARLA LISSETE</t>
+          <t>ANA KAREN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>SABORI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>AGUILEA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4491780397</t>
+          <t>6862883709</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TARCENTO #217</t>
+          <t>DEL ESTORNINO 1065</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7199,48 +7199,52 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>26-08-1996</t>
+          <t>23-03-1991</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>LISS.2484@HOTMAIL.COM</t>
+          <t>KARENSABORI03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>15-02-2026 13:27:15</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>18-02-2026 12:32:57</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>15-02-2026 13:50:40</t>
+          <t>18-02-2026 12:43:59</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>15-02-2026 13:49:20</t>
+          <t>18-02-2026 12:42:38</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7250,7 +7254,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7260,14 +7264,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26190522367020003919</t>
+          <t>26030522460890002202</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7419,12 +7423,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>341757</t>
+          <t>343528</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7434,17 +7438,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>JESUS ANDREI</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACEVES </t>
+          <t>BARRIOS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RAYNOSO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7454,75 +7458,67 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6861447478</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>CORONADO</t>
-        </is>
-      </c>
+          <t>7447521987</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10-05-1968</t>
+          <t>19-09-2011</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ALYSS.5@ICLOUD.COM</t>
+          <t>BARRIOSANDREI91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>07-02-2026 08:52:55</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>13-02-2026 16:22:11</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>07-02-2026 08:58:06</t>
+          <t>13-02-2026 16:25:18</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>07-02-2026 08:56:15</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7530,14 +7526,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26030522156700001689</t>
+          <t>26030522324160001979</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7554,12 +7550,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343527</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7569,17 +7565,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ANDRES GUADALUPE</t>
+          <t>MARIA NATALY</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BARRIOS</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7589,67 +7585,75 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6864208824</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6633828366</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>VERONA RESIDENCIAL</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>08-04-1990</t>
+          <t>16-03-1996</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BARRIOSFELIXANDRES1990@HOTMAIL.COM</t>
+          <t>CNATALY062@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>13-02-2026 16:15:25</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 12:38:37</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 16:17:17</t>
+          <t>15-02-2026 13:12:02</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>15-02-2026 13:08:39</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7657,36 +7661,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26030522323970001978</t>
+          <t>26130522366310002860</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>341854</t>
+          <t>343854</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7696,17 +7700,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FELICIANA</t>
+          <t>HECTOR ISAAC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7716,32 +7720,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6862375198</t>
+          <t>4421447271</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AV GANDARA 407</t>
+          <t>ARCO DE LA INDEPENDENCIA #131</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>07-02-1980</t>
+          <t>11-10-1994</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>LAFONDAMXL@ARAIZAHOTELES.COM</t>
+          <t>HECGRAVES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>07-02-2026 23:12:20</t>
+          <t>15-02-2026 13:30:18</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7762,17 +7766,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>08-02-2026 15:19:42</t>
+          <t>15-02-2026 13:54:06</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:09</t>
+          <t>15-02-2026 13:52:50</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7792,7 +7796,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522173240001995</t>
+          <t>26190522367050003920</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7804,24 +7808,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342137</t>
+          <t>343527</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7831,17 +7835,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CELIA </t>
+          <t>ANDRES GUADALUPE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>BARRIOS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7851,75 +7855,67 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6863468404</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEL PARAISO </t>
-        </is>
-      </c>
+          <t>6864208824</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>29-04-2004</t>
+          <t>08-04-1990</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CRUZJUAREZMARTHACELIA@GMAIL.COM</t>
+          <t>BARRIOSFELIXANDRES1990@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>09-02-2026 12:30:55</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>13-02-2026 16:15:25</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>09-02-2026 12:40:11</t>
+          <t>13-02-2026 16:17:17</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>09-02-2026 12:39:32</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7927,14 +7923,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26030522190690001723</t>
+          <t>26030522323970001978</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7951,12 +7947,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343496</t>
+          <t>341757</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7971,12 +7967,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">ACEVES </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>RAYNOSO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7986,12 +7982,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6644799843</t>
+          <t>6861447478</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">C GARCIA CUBAS 50 </t>
+          <t>CORONADO</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8001,24 +7997,20 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>17-02-1983</t>
+          <t>10-05-1968</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>KAKETITO07@GMAIL.COM</t>
+          <t>ALYSS.5@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>13-02-2026 13:35:27</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>07-02-2026 08:52:55</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8036,17 +8028,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 17:55:45</t>
+          <t>07-02-2026 08:58:06</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>16-02-2026 17:53:57</t>
+          <t>07-02-2026 08:56:15</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8056,7 +8048,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8066,7 +8058,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26120522401800007130</t>
+          <t>26030522156700001689</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8078,7 +8070,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8090,12 +8082,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343528</t>
+          <t>345228</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>87393</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8105,17 +8097,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JESUS ANDREI</t>
+          <t>JAIME NAEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BARRIOS</t>
+          <t xml:space="preserve">GAXIOLA </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8125,10 +8117,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7447521987</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6865439867</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ACAMDI 1999</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8136,56 +8132,64 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>19-09-2011</t>
+          <t>17-06-2011</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BARRIOSANDREI91@GMAIL.COM</t>
+          <t>GAXIOLAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>13-02-2026 16:22:11</t>
+          <t>20-02-2026 08:11:26</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>13-02-2026 16:25:18</t>
+          <t>20-02-2026 11:02:35</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>20-02-2026 11:01:22</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8193,36 +8197,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26030522324160001979</t>
+          <t>26030522523600002300</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>344089</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8232,17 +8236,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MARIA NATALY</t>
+          <t>IRLANDA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8252,14 +8256,10 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6633828366</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>VERONA RESIDENCIAL</t>
-        </is>
-      </c>
+          <t>6862036959</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8267,60 +8267,56 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16-03-1996</t>
+          <t>01-04-2005</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CNATALY062@GMAIL.COM</t>
+          <t>JIMENEZIRLANDA075@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>14-02-2026 12:38:37</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>16-02-2026 14:13:07</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>15-02-2026 13:12:02</t>
+          <t>16-02-2026 14:14:13</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>15-02-2026 13:08:39</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8328,36 +8324,36 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26130522366310002860</t>
+          <t>26030522390010002054</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343854</t>
+          <t>344342</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8367,17 +8363,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HECTOR ISAAC</t>
+          <t xml:space="preserve">JOSE ANDRIAN </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8387,14 +8383,10 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4421447271</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>ARCO DE LA INDEPENDENCIA #131</t>
-        </is>
-      </c>
+          <t>6865107062</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8402,60 +8394,56 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>11-10-1994</t>
+          <t>18-12-2001</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>HECGRAVES@HOTMAIL.COM</t>
+          <t>A23490139@ITMEXICALI.EDU.MX</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>15-02-2026 13:30:18</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>16-02-2026 19:20:54</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>15-02-2026 13:54:06</t>
+          <t>16-02-2026 19:22:28</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>15-02-2026 13:52:50</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8463,14 +8451,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26190522367050003920</t>
+          <t>26030522408150002080</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8487,12 +8475,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344342</t>
+          <t>344355</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8502,17 +8490,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANDRIAN </t>
+          <t>BRIZA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8522,28 +8510,28 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6865107062</t>
+          <t>6861342121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18-12-2001</t>
+          <t>28-11-2004</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A23490139@ITMEXICALI.EDU.MX</t>
+          <t>MARTINEZGONZALEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 19:20:54</t>
+          <t>16-02-2026 20:38:13</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8558,17 +8546,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>16-02-2026 19:22:28</t>
+          <t>16-02-2026 20:39:38</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8579,7 +8567,7 @@
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V61" t="inlineStr"/>
@@ -8590,14 +8578,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26030522408150002080</t>
+          <t>26030522410780002090</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8614,12 +8602,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344355</t>
+          <t>345984</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>88149</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8629,17 +8617,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BRIZA</t>
+          <t>MARTHA ISABEL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8649,7 +8637,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6861342121</t>
+          <t>6862885198</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8660,17 +8648,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>28-11-2004</t>
+          <t>12-04-1997</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>MARTINEZGONZALEZ@GMAIL.COM</t>
+          <t>MISABE12EM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 20:38:13</t>
+          <t>23-02-2026 18:28:04</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8695,12 +8683,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 20:39:38</t>
+          <t>23-02-2026 18:29:37</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -8717,7 +8705,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26030522410780002090</t>
+          <t>26030522595770002366</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8741,12 +8729,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344799</t>
+          <t>341440</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8756,17 +8744,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANA KAREN</t>
+          <t>REGINA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SABORI</t>
+          <t>MÉNDEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AGUILEA</t>
+          <t>LÓPEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8776,14 +8764,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6862883709</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>DEL ESTORNINO 1065</t>
-        </is>
-      </c>
+          <t>6862143110</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8791,17 +8775,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>23-03-1991</t>
+          <t>08-09-2009</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>KARENSABORI03@GMAIL.COM</t>
+          <t>MENDEZREGINA008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 12:32:57</t>
+          <t>05-02-2026 19:35:29</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8811,44 +8795,36 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 12:43:59</t>
+          <t>10-02-2026 19:16:47</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>18-02-2026 12:42:38</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8856,36 +8832,44 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26030522460890002202</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+          <t>26030522246320001836</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344089</t>
+          <t>343496</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8895,12 +8879,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>IRLANDA</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8915,10 +8899,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6862036959</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6644799843</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C GARCIA CUBAS 50 </t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8926,42 +8914,42 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>01-04-2005</t>
+          <t>17-02-1983</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>JIMENEZIRLANDA075@GMAIL.COM</t>
+          <t>KAKETITO07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 14:13:07</t>
+          <t>13-02-2026 13:35:27</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 14:14:13</t>
+          <t>16-02-2026 17:55:45</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -8969,13 +8957,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:53:57</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8983,19 +8979,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26030522390010002054</t>
+          <t>26120522401800007130</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9007,12 +9003,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345228</t>
+          <t>341854</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9022,17 +9018,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JAIME NAEL</t>
+          <t>FELICIANA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAXIOLA </t>
+          <t xml:space="preserve">VILLA </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9042,39 +9038,35 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6865439867</t>
+          <t>6862375198</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ACAMDI 1999</t>
+          <t>AV GANDARA 407</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>17-06-2011</t>
+          <t>07-02-1980</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>GAXIOLAVALENZUELA@GMAIL.COM</t>
+          <t>LAFONDAMXL@ARAIZAHOTELES.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>20-02-2026 08:11:26</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>07-02-2026 23:12:20</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9092,17 +9084,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-02-2026 11:02:35</t>
+          <t>08-02-2026 15:19:42</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20-02-2026 11:01:22</t>
+          <t>08-02-2026 15:10:09</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9122,7 +9114,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26030522523600002300</t>
+          <t>26170522173240001995</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9134,12 +9126,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9277,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344572</t>
+          <t>342611</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9300,17 +9292,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
+          <t>BARADA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9320,12 +9312,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6862474145</t>
+          <t>5588063125</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CALLE DE GUAYABOS 99</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9335,22 +9327,22 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17-09-2002</t>
+          <t>13-10-1985</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ANDRESSEVILLAMARTINEZ2002.COM@GMAIL.COM</t>
+          <t>EDUARDOBARADA131085@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:33:36</t>
+          <t>10-02-2026 13:20:56</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -9360,27 +9352,27 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:39:07</t>
+          <t>19-02-2026 09:59:29</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>17-02-2026 16:37:15</t>
+          <t>19-02-2026 09:57:12</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9390,7 +9382,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9400,36 +9392,36 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26030522434640002148</t>
+          <t>26280522490660006426</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344576</t>
+          <t>342137</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9439,17 +9431,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JESUS ALICIA</t>
+          <t xml:space="preserve">MARTHA CELIA </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTAMIRANO </t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9459,12 +9451,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6862340246</t>
+          <t>6863468404</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>RIO MEZCALAPA 1957</t>
+          <t xml:space="preserve">DEL PARAISO </t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9474,24 +9466,20 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>29-04-2004</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>LTF.ALICIAALTA9@GMAIL.COM</t>
+          <t>CRUZJUAREZMARTHACELIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17-02-2026 16:43:50</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 12:30:55</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9499,27 +9487,27 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>17-02-2026 16:48:49</t>
+          <t>09-02-2026 12:40:11</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>17-02-2026 16:46:32</t>
+          <t>09-02-2026 12:39:32</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9539,24 +9527,24 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26030522435320002151</t>
+          <t>26030522190690001723</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9690,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>342821</t>
+          <t>344572</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9717,17 +9705,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ALEXANDRA</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>SEVILLA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CARRASCO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9737,67 +9725,79 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6862815885</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>6862474145</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>CALLE DE GUAYABOS 99</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>23-08-1999</t>
+          <t>17-09-2002</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ANGULOALEXA23@GMAIL.COM</t>
+          <t>ANDRESSEVILLAMARTINEZ2002.COM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:09</t>
+          <t>17-02-2026 16:33:36</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-02-2026 19:03:42</t>
+          <t>17-02-2026 16:39:07</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:37:15</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9805,14 +9805,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26030522245640001834</t>
+          <t>26030522434640002148</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9829,12 +9829,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>342611</t>
+          <t>344576</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>JESUS ALICIA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BARADA</t>
+          <t xml:space="preserve">ALTAMIRANO </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9864,37 +9864,37 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5588063125</t>
+          <t>6862340246</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>RIO MEZCALAPA 1957</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>13-10-1985</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>EDUARDOBARADA131085@GMAIL.COM</t>
+          <t>LTF.ALICIAALTA9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>10-02-2026 13:20:56</t>
+          <t>17-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -9904,27 +9904,27 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>19-02-2026 09:59:29</t>
+          <t>17-02-2026 16:48:49</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>19-02-2026 09:57:12</t>
+          <t>17-02-2026 16:46:32</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9944,14 +9944,14 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26280522490660006426</t>
+          <t>26030522435320002151</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -10107,12 +10107,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>343973</t>
+          <t>342821</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JUAN RAMON</t>
+          <t>ALEXANDRA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CARRASCO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10142,28 +10142,28 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6861001108</t>
+          <t>6862815885</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>24-06-1964</t>
+          <t>23-08-1999</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ESAZUL167@GMAIL.COM</t>
+          <t>ANGULOALEXA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:01</t>
+          <t>10-02-2026 19:02:09</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10178,22 +10178,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:57</t>
+          <t>10-02-2026 19:03:42</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -10210,19 +10210,19 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26030522381380002030</t>
+          <t>26030522245640001834</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -10234,12 +10234,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>343973</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10249,17 +10249,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>JUAN RAMON</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10269,57 +10269,53 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6865903523</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>CALLE OCTAVA 712</t>
-        </is>
-      </c>
+          <t>6861001108</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>03-12-1979</t>
+          <t>24-06-1964</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>LULUNIGER@GMAIL.COM</t>
+          <t>ESAZUL167@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>16-02-2026 18:21:34</t>
+          <t>16-02-2026 08:42:01</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>16-02-2026 18:41:26</t>
+          <t>16-02-2026 08:42:57</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -10327,21 +10323,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:29:07</t>
-        </is>
-      </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10349,19 +10337,19 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26030522405340002070</t>
+          <t>26030522381380002030</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -10373,12 +10361,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>343308</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21125</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10388,17 +10376,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA </t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10408,12 +10396,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8442256431</t>
+          <t>6865903523</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ISABEL DE ARAGON 111</t>
+          <t>CALLE OCTAVA 712</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10423,20 +10411,24 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>12-02-1990</t>
+          <t>03-12-1979</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>PATTYE12182@GMAIL.COM</t>
+          <t>LULUNIGER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>12-02-2026 16:22:24</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>16-02-2026 18:21:34</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10454,17 +10446,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>13-02-2026 18:24:42</t>
+          <t>16-02-2026 18:41:26</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>13-02-2026 18:23:14</t>
+          <t>16-02-2026 18:29:07</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10484,19 +10476,11 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26190522328150003840</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
-        </is>
-      </c>
+          <t>26030522405340002070</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
           <t>499</t>
@@ -10504,24 +10488,24 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344301</t>
+          <t>344314</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10531,17 +10515,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KARLA NICOLEE</t>
+          <t>JANNETH</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10551,10 +10535,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6863620808</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>6647320627</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>CALLE OCTAVA 712</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10562,42 +10550,42 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>25-09-2003</t>
+          <t>22-03-2000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>KNICOLE.ME@GMAIL.COM</t>
+          <t>MENDOZAJANNETH59@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:36:27</t>
+          <t>16-02-2026 18:50:53</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>16-02-2026 18:43:05</t>
+          <t>16-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -10605,13 +10593,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:55:30</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10619,36 +10615,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26030522405430002071</t>
+          <t>26030522406380002074</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344314</t>
+          <t>343308</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10658,17 +10654,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JANNETH</t>
+          <t xml:space="preserve">PATRICIA </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10678,12 +10674,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6647320627</t>
+          <t>8442256431</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CALLE OCTAVA 712</t>
+          <t>ISABEL DE ARAGON 111</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10693,24 +10689,20 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22-03-2000</t>
+          <t>12-02-1990</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>MENDOZAJANNETH59@GMAIL.COM</t>
+          <t>PATTYE12182@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>16-02-2026 18:50:53</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 16:22:24</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10728,17 +10720,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>16-02-2026 18:57:38</t>
+          <t>13-02-2026 18:24:42</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>16-02-2026 18:55:30</t>
+          <t>13-02-2026 18:23:14</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10758,11 +10750,19 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26030522406380002074</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
+          <t>26190522328150003840</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>CECILIA ABIGAIL GOMEZ  HANDAL</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>499</t>
@@ -10770,12 +10770,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -11038,6 +11038,272 @@
       <c r="AC79" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>344301</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>22118</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>KARLA NICOLEE</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6863620808</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>25-09-2003</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>KNICOLE.ME@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:36:27</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:43:05</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>26030522405430002071</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>345857</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>88022</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDREA YAMILETH </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRAZAS </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6866053687</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>FRACC.MIRASOL</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>14-12-2012</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>YAMILETH2012@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:11:08</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:15:58</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:14:37</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>26030522586510002354</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -2170,12 +2170,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>279271</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>76772</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBA CRISTINA </t>
+          <t xml:space="preserve">JUAN CARLOS </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMODOVAR </t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t xml:space="preserve">REY </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2205,32 +2205,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6862238374</t>
+          <t>6561837211</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CERADA CICA 4193</t>
+          <t>FBDFG</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-06-1992</t>
+          <t>22-06-1985</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ALMODOVARALBA06@GMAIL.COM</t>
+          <t>JUANCARLOSTOVARREY1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-02-2026 05:14:54</t>
+          <t>17-02-2025 18:22:50</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2251,17 +2251,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-02-2026 05:21:38</t>
+          <t>09-02-2026 17:27:20</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>04-02-2026 05:20:34</t>
+          <t>08-02-2026 15:26:21</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2281,10 +2281,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26030522065870001511</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26010522202230003395</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2293,7 +2297,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2305,12 +2309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>334762</t>
+          <t>310112</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA MAGDALENA </t>
+          <t xml:space="preserve">RAYMUNDO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GALVEZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2340,14 +2344,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862268524</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PARAJES DE PUEBLA</t>
-        </is>
-      </c>
+          <t>6861447809</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2355,60 +2355,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-06-1973</t>
+          <t>29-12-1967</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>LUNAMALENA2473@GMAIL.COM</t>
+          <t>RAYMUNDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>14-01-2026 16:14:31</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>19-08-2025 09:08:36</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-02-2026 15:08:35</t>
+          <t>18-02-2026 08:27:18</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>05-02-2026 15:07:47</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2416,36 +2412,44 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26030522107950001586</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26020522457140001080</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Eduardo  Rivera Ramirez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>279271</t>
+          <t>340851</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>76772</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2455,17 +2459,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN CARLOS </t>
+          <t xml:space="preserve">ALBA CRISTINA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t xml:space="preserve">ALMODOVAR </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">REY </t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2475,32 +2479,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6561837211</t>
+          <t>6862238374</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FBDFG</t>
+          <t>CERADA CICA 4193</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22-06-1985</t>
+          <t>18-06-1992</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JUANCARLOSTOVARREY1985@GMAIL.COM</t>
+          <t>ALMODOVARALBA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17-02-2025 18:22:50</t>
+          <t>04-02-2026 05:14:54</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2521,17 +2525,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:20</t>
+          <t>04-02-2026 05:21:38</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>08-02-2026 15:26:21</t>
+          <t>04-02-2026 05:20:34</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2551,14 +2555,10 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26010522202230003395</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030522065870001511</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>310112</t>
+          <t>334762</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAYMUNDO </t>
+          <t xml:space="preserve">JUANA MAGDALENA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>GALVEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,10 +2614,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861447809</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6862268524</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PARAJES DE PUEBLA</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2625,56 +2629,60 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29-12-1967</t>
+          <t>24-06-1973</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>RAYMUNDOGARCIA@GMAIL.COM</t>
+          <t>LUNAMALENA2473@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19-08-2025 09:08:36</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-01-2026 16:14:31</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>18-02-2026 08:27:18</t>
+          <t>05-02-2026 15:08:35</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>05-02-2026 15:07:47</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2682,32 +2690,24 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522457140001080</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>26030522107950001586</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo  Rivera Ramirez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343491</t>
+          <t>340853</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4595,17 +4595,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZELL  </t>
+          <t xml:space="preserve">NUVIA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONDACA </t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6863457622</t>
+          <t>6861523739</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>POBLADO INDIVISO</t>
+          <t>COLONIA MEZQUITAL 4232</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25-10-2005</t>
+          <t>08-02-1988</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ITZELLMONDACA1027@GMAIL.COM</t>
+          <t>NUVIAVA742@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13-02-2026 13:16:20</t>
+          <t>04-02-2026 05:23:13</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>13-02-2026 13:20:14</t>
+          <t>04-02-2026 05:26:37</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>13-02-2026 13:19:37</t>
+          <t>04-02-2026 05:26:10</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26030522320340001971</t>
+          <t>26030522065980001512</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343492</t>
+          <t>343491</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21308</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAULA DENISSE </t>
+          <t xml:space="preserve">ITZELL  </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t xml:space="preserve">MONDACA </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6862768858</t>
+          <t>6863457622</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EJIDO GUERRERO </t>
+          <t>POBLADO INDIVISO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>28-09-1998</t>
+          <t>25-10-2005</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>DENISSE.TD@GMAIL.COM</t>
+          <t>ITZELLMONDACA1027@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13-02-2026 13:21:47</t>
+          <t>13-02-2026 13:16:20</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>13-02-2026 13:25:14</t>
+          <t>13-02-2026 13:20:14</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>13-02-2026 13:24:52</t>
+          <t>13-02-2026 13:19:37</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26030522320400001972</t>
+          <t>26030522320340001971</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340853</t>
+          <t>343492</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUVIA </t>
+          <t xml:space="preserve">PAULA DENISSE </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861523739</t>
+          <t>6862768858</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COLONIA MEZQUITAL 4232</t>
+          <t xml:space="preserve">EJIDO GUERRERO </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>08-02-1988</t>
+          <t>28-09-1998</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NUVIAVA742@GMAIL.COM</t>
+          <t>DENISSE.TD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>04-02-2026 05:23:13</t>
+          <t>13-02-2026 13:21:47</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4931,17 +4931,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>04-02-2026 05:26:37</t>
+          <t>13-02-2026 13:25:14</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>04-02-2026 05:26:10</t>
+          <t>13-02-2026 13:24:52</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26030522065980001512</t>
+          <t>26030522320400001972</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4985,12 +4985,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340719</t>
+          <t>343853</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>KARLA LISSETE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LLANES</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6865254236</t>
+          <t>4491780397</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AV. RANCHO GRANDE 1937</t>
+          <t>TARCENTO #217</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12-08-1993</t>
+          <t>26-08-1996</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LUISESOTO258@GMAIL.COM</t>
+          <t>LISS.2484@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:17:43</t>
+          <t>15-02-2026 13:27:15</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5066,17 +5066,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:20:41</t>
+          <t>15-02-2026 13:50:40</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:56</t>
+          <t>15-02-2026 13:49:20</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26030522048910001474</t>
+          <t>26190522367020003919</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5108,24 +5108,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343853</t>
+          <t>341094</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5135,17 +5135,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KARLA LISSETE</t>
+          <t>JAKELYN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>PEREDA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>LIZAOLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5155,14 +5155,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4491780397</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>TARCENTO #217</t>
-        </is>
-      </c>
+          <t>6861494317</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5170,60 +5166,56 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>26-08-1996</t>
+          <t>09-04-2010</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LISS.2484@HOTMAIL.COM</t>
+          <t>PJAKELYN67@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15-02-2026 13:27:15</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>04-02-2026 17:06:54</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>15-02-2026 13:50:40</t>
+          <t>04-02-2026 17:08:03</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>15-02-2026 13:49:20</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5231,36 +5223,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26190522367020003919</t>
+          <t>26030522081420001541</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>341441</t>
+          <t>340719</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5270,17 +5262,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CARLOS AGUSTIN</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>LLANES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5290,10 +5282,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6861409324</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6865254236</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AV. RANCHO GRANDE 1937</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5301,56 +5297,60 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>12-08-1993</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CARLOSAGUSTIN.MENDEZ@UABC.EDU.MX</t>
+          <t>LUISESOTO258@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>05-02-2026 19:35:46</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 17:17:43</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-02-2026 19:14:03</t>
+          <t>03-02-2026 17:20:41</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:19:56</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5358,18 +5358,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26030522246130001835</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522048910001474</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5513,12 +5509,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>341094</t>
+          <t>341441</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5528,17 +5524,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JAKELYN</t>
+          <t>CARLOS AGUSTIN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PEREDA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LIZAOLA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5548,28 +5544,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6861494317</t>
+          <t>6861409324</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>09-04-2010</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PJAKELYN67@GMAIL.COM</t>
+          <t>CARLOSAGUSTIN.MENDEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>04-02-2026 17:06:54</t>
+          <t>05-02-2026 19:35:46</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5584,28 +5580,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>04-02-2026 17:08:03</t>
+          <t>10-02-2026 19:14:03</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5616,14 +5612,18 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26030522081420001541</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
+          <t>26030522246130001835</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5640,12 +5640,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342396</t>
+          <t>341757</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5655,17 +5655,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCELINA </t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t xml:space="preserve">ACEVES </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>RAYNOSO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6634048799</t>
+          <t>6861447478</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SANCHEZ TABOADA</t>
+          <t>CORONADO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>09-02-1990</t>
+          <t>10-05-1968</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>MYAM-18@GMAIL.COM</t>
+          <t>ALYSS.5@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:21</t>
+          <t>07-02-2026 08:52:55</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>11-02-2026 19:01:18</t>
+          <t>07-02-2026 08:58:06</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11-02-2026 19:00:38</t>
+          <t>07-02-2026 08:56:15</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5751,19 +5751,11 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26110522275680003096</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>DIARA IVETH HERNANDEZ RADILLA</t>
-        </is>
-      </c>
+          <t>26030522156700001689</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
           <t>499</t>
@@ -5771,24 +5763,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342515</t>
+          <t>344799</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5798,17 +5790,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>ANA KAREN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t>SABORI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>AGUILEA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5818,63 +5810,67 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861587461</t>
+          <t>6862883709</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOAQUIN AMARO </t>
+          <t>DEL ESTORNINO 1065</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22-12-1987</t>
+          <t>23-03-1991</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ZORDI.EDUARDO@GMAIL.COM</t>
+          <t>KARENSABORI03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10-02-2026 05:37:41</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>18-02-2026 12:32:57</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-02-2026 05:40:22</t>
+          <t>18-02-2026 12:43:59</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>10-02-2026 05:39:54</t>
+          <t>18-02-2026 12:42:38</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5884,7 +5880,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5894,14 +5890,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26030522222310001786</t>
+          <t>26030522460890002202</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5918,12 +5914,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344799</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5933,17 +5929,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ANA KAREN</t>
+          <t xml:space="preserve">MARCELINA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SABORI</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AGUILEA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5953,12 +5949,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6862883709</t>
+          <t>6634048799</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DEL ESTORNINO 1065</t>
+          <t>SANCHEZ TABOADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5968,52 +5964,48 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-03-1991</t>
+          <t>09-02-1990</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>KARENSABORI03@GMAIL.COM</t>
+          <t>MYAM-18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-02-2026 12:32:57</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:32:21</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 12:43:59</t>
+          <t>11-02-2026 19:01:18</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>18-02-2026 12:42:38</t>
+          <t>11-02-2026 19:00:38</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6033,14 +6025,22 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26030522460890002202</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+          <t>26110522275680003096</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>DIARA IVETH HERNANDEZ RADILLA</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6057,12 +6057,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341440</t>
+          <t>342515</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>REGINA</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MÉNDEZ</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LÓPEZ</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6092,53 +6092,53 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6862143110</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6861587461</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOAQUIN AMARO </t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>08-09-2009</t>
+          <t>22-12-1987</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MENDEZREGINA008@GMAIL.COM</t>
+          <t>ZORDI.EDUARDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>05-02-2026 19:35:29</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 05:37:41</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:47</t>
+          <t>10-02-2026 05:40:22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6146,13 +6146,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:39:54</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6160,32 +6168,24 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26030522246320001836</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>laura cajera escobar palomec</t>
-        </is>
-      </c>
+          <t>26030522222310001786</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>341757</t>
+          <t>341440</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>REGINA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACEVES </t>
+          <t>MÉNDEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RAYNOSO</t>
+          <t>LÓPEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6358,14 +6358,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861447478</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>CORONADO</t>
-        </is>
-      </c>
+          <t>6862143110</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6373,60 +6369,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>10-05-1968</t>
+          <t>08-09-2009</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ALYSS.5@ICLOUD.COM</t>
+          <t>MENDEZREGINA008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>07-02-2026 08:52:55</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>05-02-2026 19:35:29</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>07-02-2026 08:58:06</t>
+          <t>10-02-2026 19:16:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>07-02-2026 08:56:15</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6434,19 +6426,27 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26030522156700001689</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26030522246320001836</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>laura cajera escobar palomec</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>341854</t>
+          <t>344342</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6473,17 +6473,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FELICIANA</t>
+          <t xml:space="preserve">JOSE ANDRIAN </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLA </t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6493,75 +6493,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6862375198</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>AV GANDARA 407</t>
-        </is>
-      </c>
+          <t>6865107062</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>07-02-1980</t>
+          <t>18-12-2001</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>LAFONDAMXL@ARAIZAHOTELES.COM</t>
+          <t>A23490139@ITMEXICALI.EDU.MX</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>07-02-2026 23:12:20</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>16-02-2026 19:20:54</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>08-02-2026 15:19:42</t>
+          <t>16-02-2026 19:22:28</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>08-02-2026 15:10:09</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6569,36 +6561,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170522173240001995</t>
+          <t>26030522408150002080</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344342</t>
+          <t>344355</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6608,17 +6600,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ANDRIAN </t>
+          <t>BRIZA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6628,28 +6620,28 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6865107062</t>
+          <t>6861342121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18-12-2001</t>
+          <t>28-11-2004</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>A23490139@ITMEXICALI.EDU.MX</t>
+          <t>MARTINEZGONZALEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 19:20:54</t>
+          <t>16-02-2026 20:38:13</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6664,17 +6656,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 19:22:28</t>
+          <t>16-02-2026 20:39:38</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6685,7 +6677,7 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -6696,14 +6688,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26030522408150002080</t>
+          <t>26030522410780002090</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6720,12 +6712,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344355</t>
+          <t>345228</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>87393</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6735,17 +6727,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BRIZA</t>
+          <t>JAIME NAEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GAXIOLA </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6755,67 +6747,79 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6861342121</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6865439867</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ACAMDI 1999</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>28-11-2004</t>
+          <t>17-06-2011</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MARTINEZGONZALEZ@GMAIL.COM</t>
+          <t>GAXIOLAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 20:38:13</t>
+          <t>20-02-2026 08:11:26</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 20:39:38</t>
+          <t>20-02-2026 11:02:35</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>20-02-2026 11:01:22</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6823,14 +6827,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26030522410780002090</t>
+          <t>26030522523600002300</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6982,12 +6986,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345228</t>
+          <t>341854</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6997,17 +7001,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JAIME NAEL</t>
+          <t>FELICIANA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAXIOLA </t>
+          <t xml:space="preserve">VILLA </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7017,39 +7021,35 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6865439867</t>
+          <t>6862375198</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ACAMDI 1999</t>
+          <t>AV GANDARA 407</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17-06-2011</t>
+          <t>07-02-1980</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>GAXIOLAVALENZUELA@GMAIL.COM</t>
+          <t>LAFONDAMXL@ARAIZAHOTELES.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>20-02-2026 08:11:26</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>07-02-2026 23:12:20</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7067,17 +7067,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>20-02-2026 11:02:35</t>
+          <t>08-02-2026 15:19:42</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>20-02-2026 11:01:22</t>
+          <t>08-02-2026 15:10:09</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26030522523600002300</t>
+          <t>26170522173240001995</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7248,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342137</t>
+          <t>342220</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA CELIA </t>
+          <t>VENEZIA MILDRETH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863468404</t>
+          <t>6863374140</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEL PARAISO </t>
+          <t>PUERT DEL SOL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>29-04-2004</t>
+          <t>15-01-2007</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CRUZJUAREZMARTHACELIA@GMAIL.COM</t>
+          <t>VENEZIACORRAL9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>09-02-2026 12:30:55</t>
+          <t>09-02-2026 15:45:41</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>09-02-2026 12:40:11</t>
+          <t>09-02-2026 15:48:29</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>09-02-2026 12:39:32</t>
+          <t>09-02-2026 15:47:18</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26030522190690001723</t>
+          <t>26030522196150001735</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7383,12 +7383,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342511</t>
+          <t>342137</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7398,17 +7398,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAIME ARTURO </t>
+          <t xml:space="preserve">MARTHA CELIA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVERA </t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7418,67 +7418,63 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6861179222</t>
+          <t>6863468404</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIO CONGO </t>
+          <t xml:space="preserve">DEL PARAISO </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>27-03-1985</t>
+          <t>29-04-2004</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>JAIME.GARCIARIVERA@HOTMAIL.COM</t>
+          <t>CRUZJUAREZMARTHACELIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 05:25:26</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 12:30:55</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 05:29:34</t>
+          <t>09-02-2026 12:40:11</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10-02-2026 05:28:54</t>
+          <t>09-02-2026 12:39:32</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7488,7 +7484,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7498,19 +7494,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26030522222120001785</t>
+          <t>26030522190690001723</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7522,12 +7518,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342220</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7537,17 +7533,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VENEZIA MILDRETH</t>
+          <t xml:space="preserve">JAIME ARTURO </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CORRAL</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7557,63 +7553,67 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6863374140</t>
+          <t>6861179222</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PUERT DEL SOL</t>
+          <t xml:space="preserve">RIO CONGO </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>15-01-2007</t>
+          <t>27-03-1985</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>VENEZIACORRAL9@GMAIL.COM</t>
+          <t>JAIME.GARCIARIVERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>09-02-2026 15:45:41</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>10-02-2026 05:25:26</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>09-02-2026 15:48:29</t>
+          <t>10-02-2026 05:29:34</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>09-02-2026 15:47:18</t>
+          <t>10-02-2026 05:28:54</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7633,19 +7633,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26030522196150001735</t>
+          <t>26030522222120001785</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7657,12 +7657,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342507</t>
+          <t>346254</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7672,17 +7672,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYNTHIA </t>
+          <t>REYNALDO ENRIQUE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PIÑA </t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TERAN</t>
+          <t>RODRÍGUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7692,35 +7692,39 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6461790091</t>
+          <t>6862674775</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MAR BALTICO</t>
+          <t>VALLE DEL PEDREGAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>09-12-1976</t>
+          <t>14-05-1999</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CINTHYATERAN@GMAIL.COM</t>
+          <t>ENRIQU145@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>09-02-2026 22:00:59</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>24-02-2026 17:25:17</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7738,17 +7742,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 09:11:58</t>
+          <t>26-02-2026 17:41:49</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 09:10:45</t>
+          <t>26-02-2026 17:41:15</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7768,11 +7772,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26080522226680002378</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26030522690340002553</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>CLARIBEL AGUIRRE GONZALES</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -7792,12 +7804,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342540</t>
+          <t>342507</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7807,17 +7819,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OSCAR FERNANDO</t>
+          <t xml:space="preserve">CYNTHIA </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">PIÑA </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>TERAN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7827,32 +7839,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6863662750</t>
+          <t>6461790091</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AV. SAN PABLO 1656</t>
+          <t>MAR BALTICO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>21-11-2000</t>
+          <t>09-12-1976</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>RAMIREZ2167@HOTMAIL.COM</t>
+          <t>CINTHYATERAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:56:37</t>
+          <t>09-02-2026 22:00:59</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7873,7 +7885,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10-02-2026 08:01:48</t>
+          <t>10-02-2026 09:11:58</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7883,7 +7895,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>10-02-2026 08:01:02</t>
+          <t>10-02-2026 09:10:45</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7903,7 +7915,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26030522224890001794</t>
+          <t>26080522226680002378</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -7915,24 +7927,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343372</t>
+          <t>342540</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7942,17 +7954,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL DANIEL </t>
+          <t>OSCAR FERNANDO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7962,12 +7974,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8446722943</t>
+          <t>6863662750</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>JUAN VERLANGA</t>
+          <t>AV. SAN PABLO 1656</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7977,17 +7989,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12-02-1990</t>
+          <t>21-11-2000</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ANGELGOOMEZ6@GMAIL.COM</t>
+          <t>RAMIREZ2167@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>12-02-2026 18:39:44</t>
+          <t>10-02-2026 07:56:37</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8008,17 +8020,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:04:43</t>
+          <t>10-02-2026 08:01:48</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:35</t>
+          <t>10-02-2026 08:01:02</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8038,7 +8050,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26190522325570003826</t>
+          <t>26030522224890001794</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8050,24 +8062,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343527</t>
+          <t>342611</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8077,17 +8089,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ANDRES GUADALUPE</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BARRIOS</t>
+          <t>BARADA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8097,10 +8109,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6864208824</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>5588063125</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8108,56 +8124,64 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>08-04-1990</t>
+          <t>13-10-1985</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BARRIOSFELIXANDRES1990@HOTMAIL.COM</t>
+          <t>EDUARDOBARADA131085@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>13-02-2026 16:15:25</t>
+          <t>10-02-2026 13:20:56</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>13-02-2026 16:17:17</t>
+          <t>19-02-2026 09:59:29</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>19-02-2026 09:57:12</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8165,36 +8189,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26030522323970001978</t>
+          <t>26280522490660006426</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>346254</t>
+          <t>343372</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>88419</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8204,17 +8228,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>REYNALDO ENRIQUE</t>
+          <t xml:space="preserve">ANGEL DANIEL </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RODRÍGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8224,12 +8248,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6862674775</t>
+          <t>8446722943</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VALLE DEL PEDREGAL</t>
+          <t>JUAN VERLANGA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8239,24 +8263,20 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>14-05-1999</t>
+          <t>12-02-1990</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ENRIQU145@GMAIL.COM</t>
+          <t>ANGELGOOMEZ6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>24-02-2026 17:25:17</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:39:44</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8274,17 +8294,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>26-02-2026 17:41:49</t>
+          <t>13-02-2026 17:04:43</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>26-02-2026 17:41:15</t>
+          <t>13-02-2026 17:03:35</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8304,19 +8324,11 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26030522690340002553</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>CLARIBEL AGUIRRE GONZALES</t>
-        </is>
-      </c>
+          <t>26190522325570003826</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
           <t>499</t>
@@ -8336,12 +8348,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342821</t>
+          <t>343527</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8351,17 +8363,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ALEXANDRA</t>
+          <t>ANDRES GUADALUPE</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>BARRIOS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CARRASCO</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8371,28 +8383,28 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6862815885</t>
+          <t>6864208824</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>23-08-1999</t>
+          <t>08-04-1990</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ANGULOALEXA23@GMAIL.COM</t>
+          <t>BARRIOSFELIXANDRES1990@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:09</t>
+          <t>13-02-2026 16:15:25</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8407,28 +8419,28 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-02-2026 19:03:42</t>
+          <t>13-02-2026 16:17:17</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
@@ -8439,19 +8451,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26030522245640001834</t>
+          <t>26030522323970001978</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8463,12 +8475,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343072</t>
+          <t>346878</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>89043</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8478,17 +8490,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>BRAYAN</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>MATEO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8498,14 +8510,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6861700652</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2807 RIO CONCEPCION</t>
-        </is>
-      </c>
+          <t>6862358158</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8513,60 +8521,56 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>28-11-1981</t>
+          <t>16-06-2007</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MORENOKARON@HOTMAIL.COM</t>
+          <t>BRYANDEGUEZMAT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>11-02-2026 17:56:14</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>27-02-2026 08:44:41</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-02-2026 16:42:48</t>
+          <t>27-02-2026 08:51:02</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:42:14</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8574,27 +8578,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26030522324620001980</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>CLARIBEL AGUIRRE GONZALES</t>
-        </is>
-      </c>
+          <t>26030522706840002584</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8606,12 +8602,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>342611</t>
+          <t>346961</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>89126</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8621,17 +8617,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO </t>
+          <t>RAUL ALEJANDRO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BARADA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8641,12 +8637,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5588063125</t>
+          <t>6862147926</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>BUGAMBILIAS</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8656,22 +8652,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>13-10-1985</t>
+          <t>19-08-1984</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>EDUARDOBARADA131085@GMAIL.COM</t>
+          <t>RAULALEJANDROGARCIABARRERA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>10-02-2026 13:20:56</t>
+          <t>27-02-2026 14:40:51</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -8681,27 +8677,27 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>19-02-2026 09:59:29</t>
+          <t>27-02-2026 14:48:58</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>19-02-2026 09:57:12</t>
+          <t>27-02-2026 14:48:03</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8711,7 +8707,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8721,36 +8717,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26280522490660006426</t>
+          <t>26030522712980002599</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>342582</t>
+          <t>342821</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8760,17 +8756,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR NESTOR </t>
+          <t>ALEXANDRA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARDIN </t>
+          <t>CARRASCO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8780,32 +8776,28 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6865100009</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>ENCINAS ESTE 401</t>
-        </is>
-      </c>
+          <t>6862815885</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>29-09-1989</t>
+          <t>23-08-1999</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>VICTOR.GONZALEZ.SARDIN@GMAIL.COM</t>
+          <t>ANGULOALEXA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>10-02-2026 11:21:31</t>
+          <t>10-02-2026 19:02:09</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8815,22 +8807,22 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10-02-2026 11:26:43</t>
+          <t>10-02-2026 19:03:42</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8838,21 +8830,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>10-02-2026 11:25:25</t>
-        </is>
-      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8860,36 +8844,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26030522229100001802</t>
+          <t>26030522245640001834</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342947</t>
+          <t>343072</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8899,17 +8883,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ROSALBA</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BOJORQUEZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8919,32 +8903,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6863931287</t>
+          <t>6861700652</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>RIO MEZCALAPA  Y OCTAVA 2941</t>
+          <t>2807 RIO CONCEPCION</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>24-08-1976</t>
+          <t>28-11-1981</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>HERNANDEZBOJORQUE@GMAIL.COM</t>
+          <t>MORENOKARON@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>11-02-2026 11:45:04</t>
+          <t>11-02-2026 17:56:14</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8965,17 +8949,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>11-02-2026 11:54:16</t>
+          <t>13-02-2026 16:42:48</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>11-02-2026 11:52:48</t>
+          <t>13-02-2026 16:42:14</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -8985,7 +8969,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -8995,11 +8979,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26030522262490001876</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26030522324620001980</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>CLARIBEL AGUIRRE GONZALES</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>499</t>
@@ -9007,24 +8999,24 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>343008</t>
+          <t>342582</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9034,17 +9026,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t xml:space="preserve">VICTOR NESTOR </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AGUILERA</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">SARDIN </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9054,12 +9046,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6421499467</t>
+          <t>6865100009</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>VALLE DE PEDREGAL</t>
+          <t>ENCINAS ESTE 401</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9069,48 +9061,52 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>29-09-1989</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ERICKAGUILERAMENDOZA14@GMAIL.COM</t>
+          <t>VICTOR.GONZALEZ.SARDIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>11-02-2026 15:19:20</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>10-02-2026 11:21:31</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>11-02-2026 15:24:43</t>
+          <t>10-02-2026 11:26:43</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>11-02-2026 15:23:47</t>
+          <t>10-02-2026 11:25:25</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9120,7 +9116,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -9130,36 +9126,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26030522266380001884</t>
+          <t>26030522229100001802</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>346878</t>
+          <t>342947</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>89043</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9169,17 +9165,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BRAYAN</t>
+          <t>ROSALBA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MATEO</t>
+          <t>BOJORQUEZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9189,67 +9185,75 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6862358158</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6863931287</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>RIO MEZCALAPA  Y OCTAVA 2941</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16-06-2007</t>
+          <t>24-08-1976</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BRYANDEGUEZMAT@GMAIL.COM</t>
+          <t>HERNANDEZBOJORQUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>27-02-2026 08:44:41</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>11-02-2026 11:45:04</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>27-02-2026 08:51:02</t>
+          <t>11-02-2026 11:54:16</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>11-02-2026 11:52:48</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9257,36 +9261,36 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26030522706840002584</t>
+          <t>26030522262490001876</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>346961</t>
+          <t>343008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>89126</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9296,17 +9300,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RAUL ALEJANDRO</t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AGUILERA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9316,12 +9320,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6862147926</t>
+          <t>6421499467</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BUGAMBILIAS</t>
+          <t>VALLE DE PEDREGAL</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9331,24 +9335,20 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>19-08-1984</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>RAULALEJANDROGARCIABARRERA7@GMAIL.COM</t>
+          <t>ERICKAGUILERAMENDOZA14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>27-02-2026 14:40:51</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 15:19:20</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9366,17 +9366,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>27-02-2026 14:48:58</t>
+          <t>11-02-2026 15:24:43</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>27-02-2026 14:48:03</t>
+          <t>11-02-2026 15:23:47</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26030522712980002599</t>
+          <t>26030522266380001884</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -10202,12 +10202,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>343973</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MARIA NATALY</t>
+          <t>JUAN RAMON</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10237,75 +10237,67 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6633828366</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>VERONA RESIDENCIAL</t>
-        </is>
-      </c>
+          <t>6861001108</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16-03-1996</t>
+          <t>24-06-1964</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CNATALY062@GMAIL.COM</t>
+          <t>ESAZUL167@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>14-02-2026 12:38:37</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>16-02-2026 08:42:01</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>15-02-2026 13:12:02</t>
+          <t>16-02-2026 08:42:57</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>15-02-2026 13:08:39</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10313,36 +10305,36 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26130522366310002860</t>
+          <t>26030522381380002030</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>343854</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10352,17 +10344,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HECTOR ISAAC</t>
+          <t>MARIA NATALY</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10372,32 +10364,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4421447271</t>
+          <t>6633828366</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARCO DE LA INDEPENDENCIA #131</t>
+          <t>VERONA RESIDENCIAL</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>11-10-1994</t>
+          <t>16-03-1996</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>HECGRAVES@HOTMAIL.COM</t>
+          <t>CNATALY062@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>15-02-2026 13:30:18</t>
+          <t>14-02-2026 12:38:37</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -10418,7 +10410,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>15-02-2026 13:54:06</t>
+          <t>15-02-2026 13:12:02</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10428,7 +10420,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>15-02-2026 13:52:50</t>
+          <t>15-02-2026 13:08:39</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10438,7 +10430,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -10448,7 +10440,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26190522367050003920</t>
+          <t>26130522366310002860</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
@@ -10472,12 +10464,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>343973</t>
+          <t>343854</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10487,17 +10479,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JUAN RAMON</t>
+          <t>HECTOR ISAAC</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10507,10 +10499,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6861001108</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>4421447271</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ARCO DE LA INDEPENDENCIA #131</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10518,56 +10514,60 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>24-06-1964</t>
+          <t>11-10-1994</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ESAZUL167@GMAIL.COM</t>
+          <t>HECGRAVES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:01</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 13:30:18</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:57</t>
+          <t>15-02-2026 13:54:06</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>15-02-2026 13:52:50</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10575,36 +10575,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26030522381380002030</t>
+          <t>26190522367050003920</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344511</t>
+          <t>346815</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>88980</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">CECILIA </t>
+          <t>LUIS MANUEL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>NAFARRATE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PAREDONES</t>
+          <t>ZAMARRIPA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10634,79 +10634,67 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6861089943</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>NUEVO MEXICALI</t>
-        </is>
-      </c>
+          <t>6862567143</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>03-04-1984</t>
+          <t>01-02-1984</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>VILLALOBOSCECILIA910@GMAIL.COM</t>
+          <t>LUISNAFARRATE84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>17-02-2026 15:02:45</t>
+          <t>26-02-2026 18:44:31</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>anualidad LE 300</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>17-02-2026 15:11:53</t>
+          <t>26-02-2026 18:46:17</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>17-02-2026 15:09:49</t>
-        </is>
-      </c>
+          <t>26-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10714,36 +10702,36 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26030522430860002135</t>
+          <t>26030522693720002559</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>344572</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10753,17 +10741,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10773,32 +10761,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6862474145</t>
+          <t>6865903523</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CALLE DE GUAYABOS 99</t>
+          <t>CALLE OCTAVA 712</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>17-09-2002</t>
+          <t>03-12-1979</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ANDRESSEVILLAMARTINEZ2002.COM@GMAIL.COM</t>
+          <t>LULUNIGER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>17-02-2026 16:33:36</t>
+          <t>16-02-2026 18:21:34</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -10823,17 +10811,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>17-02-2026 16:39:07</t>
+          <t>16-02-2026 18:41:26</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>17-02-2026 16:37:15</t>
+          <t>16-02-2026 18:29:07</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -10853,7 +10841,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26030522434640002148</t>
+          <t>26030522405340002070</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
@@ -10865,7 +10853,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -10877,12 +10865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344576</t>
+          <t>344314</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10892,17 +10880,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JESUS ALICIA</t>
+          <t>JANNETH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTAMIRANO </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10912,12 +10900,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6862340246</t>
+          <t>6647320627</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>RIO MEZCALAPA 1957</t>
+          <t>CALLE OCTAVA 712</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10927,22 +10915,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>22-03-2000</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>LTF.ALICIAALTA9@GMAIL.COM</t>
+          <t>MENDOZAJANNETH59@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:43:50</t>
+          <t>16-02-2026 18:50:53</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10952,27 +10940,27 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:48:49</t>
+          <t>16-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:46:32</t>
+          <t>16-02-2026 18:55:30</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10992,36 +10980,36 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26030522435320002151</t>
+          <t>26030522406380002074</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>346815</t>
+          <t>344360</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>88980</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11031,17 +11019,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LUIS MANUEL</t>
+          <t>JAVIER</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NAFARRATE</t>
+          <t>PERALTA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ZAMARRIPA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11051,7 +11039,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6862567143</t>
+          <t>6864731620</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -11062,22 +11050,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>01-02-1984</t>
+          <t>19-09-1999</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>LUISNAFARRATE84@GMAIL.COM</t>
+          <t>GALACTIC.CYANESCENS99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>26-02-2026 18:44:31</t>
+          <t>16-02-2026 20:57:17</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -11087,28 +11075,28 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>26-02-2026 18:46:17</t>
+          <t>16-02-2026 21:00:34</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>26-03-2027 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V80" t="inlineStr"/>
@@ -11119,14 +11107,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26030522693720002559</t>
+          <t>26030522411120002091</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11413,12 +11401,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>344511</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>22328</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11428,17 +11416,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t xml:space="preserve">CECILIA </t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>PAREDONES</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11448,12 +11436,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6865903523</t>
+          <t>6861089943</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CALLE OCTAVA 712</t>
+          <t>NUEVO MEXICALI</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11463,17 +11451,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>03-12-1979</t>
+          <t>03-04-1984</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>LULUNIGER@GMAIL.COM</t>
+          <t>VILLALOBOSCECILIA910@GMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>16-02-2026 18:21:34</t>
+          <t>17-02-2026 15:02:45</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11498,17 +11486,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>16-02-2026 18:41:26</t>
+          <t>17-02-2026 15:11:53</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>16-02-2026 18:29:07</t>
+          <t>17-02-2026 15:09:49</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11528,7 +11516,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26030522405340002070</t>
+          <t>26030522430860002135</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
@@ -11540,24 +11528,24 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>344314</t>
+          <t>344572</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11567,17 +11555,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JANNETH</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>SEVILLA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11587,32 +11575,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6647320627</t>
+          <t>6862474145</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CALLE OCTAVA 712</t>
+          <t>CALLE DE GUAYABOS 99</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>22-03-2000</t>
+          <t>17-09-2002</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>MENDOZAJANNETH59@GMAIL.COM</t>
+          <t>ANDRESSEVILLAMARTINEZ2002.COM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>16-02-2026 18:50:53</t>
+          <t>17-02-2026 16:33:36</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11637,17 +11625,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>16-02-2026 18:57:38</t>
+          <t>17-02-2026 16:39:07</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>16-02-2026 18:55:30</t>
+          <t>17-02-2026 16:37:15</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -11667,7 +11655,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26030522406380002074</t>
+          <t>26030522434640002148</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr"/>
@@ -11679,7 +11667,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -11691,12 +11679,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>344360</t>
+          <t>344576</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11706,17 +11694,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JAVIER</t>
+          <t>JESUS ALICIA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PERALTA</t>
+          <t xml:space="preserve">ALTAMIRANO </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11726,28 +11714,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6864731620</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>6862340246</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>RIO MEZCALAPA 1957</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>19-09-1999</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>GALACTIC.CYANESCENS99@GMAIL.COM</t>
+          <t>LTF.ALICIAALTA9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>16-02-2026 20:57:17</t>
+          <t>17-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -11757,36 +11749,44 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>16-02-2026 21:00:34</t>
+          <t>17-02-2026 16:48:49</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:46:32</t>
+        </is>
+      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11794,24 +11794,24 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26030522411120002091</t>
+          <t>26030522435320002151</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -12493,12 +12493,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>345857</t>
+          <t>346450</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>88022</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12508,17 +12508,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA YAMILETH </t>
+          <t xml:space="preserve">YAMEL YARELI </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRAZAS </t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6866053687</t>
+          <t>6645966637</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>FRACC.MIRASOL</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -12543,17 +12543,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>14-12-2012</t>
+          <t>21-02-1999</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>YAMILETH2012@GMAIL.COM</t>
+          <t>COTOOJEDA96@GMAIL.COM</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>23-02-2026 16:11:08</t>
+          <t>25-02-2026 12:26:05</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -12578,17 +12578,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>23-02-2026 16:15:58</t>
+          <t>25-02-2026 17:12:43</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>23-02-2026 16:14:37</t>
+          <t>25-02-2026 17:11:56</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -12608,10 +12608,14 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>26030522586510002354</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr"/>
+          <t>26130522659390003540</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr">
         <is>
@@ -12620,7 +12624,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -12632,12 +12636,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>346450</t>
+          <t>346580</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>88615</t>
+          <t>88745</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12647,17 +12651,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAMEL YARELI </t>
+          <t>LORENZO CARLOS</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -12667,57 +12671,53 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6645966637</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6864275211</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>21-02-1999</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>COTOOJEDA96@GMAIL.COM</t>
+          <t>LORENZOMARTINEZ21MTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>25-02-2026 12:26:05</t>
+          <t>25-02-2026 18:59:34</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>25-02-2026 17:12:43</t>
+          <t>25-02-2026 19:00:39</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -12725,21 +12725,13 @@
           <t>25-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>25-02-2026 17:11:56</t>
-        </is>
-      </c>
+      <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12747,23 +12739,19 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>26130522659390003540</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030522664880002500</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -12775,12 +12763,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>346580</t>
+          <t>345857</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>88745</t>
+          <t>88022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12790,17 +12778,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LORENZO CARLOS</t>
+          <t xml:space="preserve">ANDREA YAMILETH </t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">TERRAZAS </t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -12810,67 +12798,79 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>6864275211</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>6866053687</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>FRACC.MIRASOL</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>21-01-1999</t>
+          <t>14-12-2012</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>LORENZOMARTINEZ21MTZ@GMAIL.COM</t>
+          <t>YAMILETH2012@GMAIL.COM</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>25-02-2026 18:59:34</t>
+          <t>23-02-2026 16:11:08</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>25-02-2026 19:00:39</t>
+          <t>23-02-2026 16:15:58</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:14:37</t>
+        </is>
+      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W93" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12878,19 +12878,19 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>26030522664880002500</t>
+          <t>26030522586510002354</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347573</t>
+          <t>310968</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>ESTHER JANETH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863493329</t>
+          <t>6861719313</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10-02-1998</t>
+          <t>25-07-1995</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MAXI1002_@OUTLOOK.ES</t>
+          <t>JANETHMACHADOV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 13:46:37</t>
+          <t>25-08-2025 13:52:20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -659,18 +659,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 13:47:59</t>
+          <t>03-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,10 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26030522793590002677</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26030522852630002805</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -705,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347417</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>BRAULIO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,10 +744,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6601593137</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6863669528</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -751,56 +759,64 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-08-1961</t>
+          <t>16-11-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NEGROSOMEX@ICLOUD.COM</t>
+          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:20:27</t>
+          <t>27-07-2023 11:07:51</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:23:24</t>
+          <t>03-03-2026 21:18:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:17</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,24 +824,24 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522782180002649</t>
+          <t>26010522862050005600</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -975,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347592</t>
+          <t>347417</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89757</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAYARA </t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GAMEZ</t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,33 +1026,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863949303</t>
+          <t>6601593137</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>03-02-1996</t>
+          <t>10-08-1961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DAYARA.GAMEZ@GMAIL.COM</t>
+          <t>NEGROSOMEX@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:30:37</t>
+          <t>02-03-2026 07:20:27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1046,17 +1062,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:32:26</t>
+          <t>02-03-2026 07:23:24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1067,7 +1083,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1078,19 +1094,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26030522795050002683</t>
+          <t>26030522782180002649</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1102,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>347573</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>89738</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LUIS ROBERTO</t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,7 +1153,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6151040574</t>
+          <t>6863493329</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,17 +1164,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-11-2006</t>
+          <t>10-02-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+          <t>MAXI1002_@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:11</t>
+          <t>02-03-2026 13:46:37</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1183,7 +1199,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:49</t>
+          <t>02-03-2026 13:47:59</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1194,7 +1210,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1205,7 +1221,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522815780002725</t>
+          <t>26030522793590002677</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1217,24 +1233,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>187165</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>84672</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1244,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>REY ALEXANDER</t>
+          <t>AXEL NOE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RENDON</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>VILCHIS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1264,7 +1280,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6151097298</t>
+          <t>6531608871</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,17 +1291,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06-01-2006</t>
+          <t>12-07-2012</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>REYALEXSAN06@GMAIL.COM</t>
+          <t>AXEL2011ZV7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:06:58</t>
+          <t>27-07-2023 08:16:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1310,18 +1326,18 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:48</t>
+          <t>03-03-2026 19:31:55</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1332,7 +1348,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030522815370002723</t>
+          <t>26030522859090002821</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1356,12 +1372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347559</t>
+          <t>347592</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>89757</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t xml:space="preserve">DAYARA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>GAMEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1391,14 +1407,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862120974</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AV. RIO SANTA CRUZ 2756</t>
-        </is>
-      </c>
+          <t>6863949303</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1406,32 +1418,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-01-1970</t>
+          <t>03-02-1996</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
+          <t>DAYARA.GAMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:09</t>
+          <t>02-03-2026 14:30:37</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1441,7 +1453,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:22:15</t>
+          <t>02-03-2026 14:32:26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1449,21 +1461,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 13:20:14</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26030522792910002676</t>
+          <t>26030522795050002683</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1483,12 +1487,798 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348041</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90206</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANA </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6863457525</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23-06-2007</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MMICHELL650@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:23:58</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:26:28</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26030522839830002778</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347559</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89724</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ROSA MARIA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AYALA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6862120974</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AV. RIO SANTA CRUZ 2756</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>04-01-1970</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:15:09</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:22:15</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:20:14</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26030522792910002676</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347860</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90025</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>REY ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALCALA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6151097298</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>06-01-2006</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>REYALEXSAN06@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:06:58</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:09:48</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26030522815370002723</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347863</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90028</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LUIS ROBERTO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DE LA FUENTE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MENDEZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6151040574</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>14-11-2006</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:12:11</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:14:49</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26030522815780002725</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347935</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90100</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRITIAN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6861367828</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AV. RIO TEPEYAC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12-09-1998</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>HERLO.ALEXIS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:49:56</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:57:29</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:56:20</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26030522823980002754</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348248</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90413</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SERGIO ALFREDO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MONARREZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AGUIRRE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6862116838</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>21-04-1987</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SMONARREZ@PROTONMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:54:51</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:57:27</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26030522856880002815</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>310968</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ESTHER JANETH</t>
+          <t>BRAULIO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,43 +613,47 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6861719313</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6863669528</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25-07-1995</t>
+          <t>16-11-2005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JANETHMACHADOV@GMAIL.COM</t>
+          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25-08-2025 13:52:20</t>
+          <t>27-07-2023 11:07:51</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,7 +663,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 17:55:45</t>
+          <t>03-03-2026 21:18:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,13 +671,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:17</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,14 +693,10 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26030522852630002805</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26010522862050005600</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -709,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>187200</t>
+          <t>187165</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>84672</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BRAULIO</t>
+          <t>AXEL NOE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>RENDON</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>VILCHIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,14 +752,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863669528</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ASCD</t>
-        </is>
-      </c>
+          <t>6531608871</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -759,32 +763,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-11-2005</t>
+          <t>12-07-2012</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
+          <t>AXEL2011ZV7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27-07-2023 11:07:51</t>
+          <t>27-07-2023 08:16:44</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -794,7 +798,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:48</t>
+          <t>03-03-2026 19:31:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -802,21 +806,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>03-03-2026 21:18:17</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -824,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26010522862050005600</t>
+          <t>26030522859090002821</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -836,24 +832,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>331568</t>
+          <t>347516</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR </t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALDERON </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PASOS</t>
+          <t>LARIOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,14 +879,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6861194706</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6864601573</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -898,32 +890,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06-09-1979</t>
+          <t>10-09-2004</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>VCALDERON@NORTECHWATER.COM</t>
+          <t>CHRISTIAN.MARTINEZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-01-2026 14:59:23</t>
+          <t>02-03-2026 11:48:53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -933,29 +925,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:18</t>
+          <t>04-03-2026 12:57:38</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:04:29</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -963,12 +947,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522810100001487</t>
+          <t>26030522881000002857</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -979,24 +963,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347417</t>
+          <t>347521</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>YITZEL ARACELY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t>VILLARRAL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,33 +1010,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6601593137</t>
+          <t>6862765502</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-08-1961</t>
+          <t>27-04-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NEGROSOMEX@ICLOUD.COM</t>
+          <t>YITZELVILLAREAL0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:20:27</t>
+          <t>02-03-2026 12:02:09</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1062,28 +1046,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:23:24</t>
+          <t>04-03-2026 12:59:21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1094,19 +1078,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26030522782180002649</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26030522881050002858</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1118,12 +1106,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347573</t>
+          <t>347467</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>89632</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1121,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>MARÍA MONSERRAT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,67 +1141,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863493329</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6863453919</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PASEOL DEL SOL</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-02-1998</t>
+          <t>05-08-1999</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MAXI1002_@OUTLOOK.ES</t>
+          <t>MONSERRAT.AYALA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:46:37</t>
+          <t>02-03-2026 09:42:10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:47:59</t>
+          <t>04-03-2026 17:20:31</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:19:44</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,19 +1221,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522793590002677</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26030522890160002869</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>187165</t>
+          <t>310968</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84672</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AXEL NOE</t>
+          <t>ESTHER JANETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RENDON</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VILCHIS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,28 +1284,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6531608871</t>
+          <t>6861719313</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-07-2012</t>
+          <t>25-07-1995</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AXEL2011ZV7@GMAIL.COM</t>
+          <t>JANETHMACHADOV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>27-07-2023 08:16:44</t>
+          <t>25-08-2025 13:52:20</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1326,7 +1330,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:55</t>
+          <t>03-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1337,7 +1341,7 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1348,10 +1352,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030522859090002821</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26030522852630002805</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1372,12 +1380,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347592</t>
+          <t>347417</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89757</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1395,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAYARA </t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GAMEZ</t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,33 +1415,33 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863949303</t>
+          <t>6601593137</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>03-02-1996</t>
+          <t>10-08-1961</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DAYARA.GAMEZ@GMAIL.COM</t>
+          <t>NEGROSOMEX@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 14:30:37</t>
+          <t>02-03-2026 07:20:27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1443,17 +1451,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 14:32:26</t>
+          <t>02-03-2026 07:23:24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1464,7 +1472,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1475,19 +1483,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26030522795050002683</t>
+          <t>26030522782180002649</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1499,12 +1507,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348041</t>
+          <t>347538</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,17 +1522,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANA </t>
+          <t>MINERVA YISSEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1534,10 +1542,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6863457525</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6865448260</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PASEOS DEL SOL</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1545,56 +1557,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-06-2007</t>
+          <t>28-12-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MMICHELL650@GMAIL.COM</t>
+          <t>YISSEL.LOPEZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 13:23:58</t>
+          <t>02-03-2026 12:33:14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 13:26:28</t>
+          <t>04-03-2026 17:15:17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:14:20</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1602,19 +1622,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26030522839830002778</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26030522889750002868</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1626,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347559</t>
+          <t>347573</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>89738</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1641,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1661,47 +1685,43 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6862120974</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AV. RIO SANTA CRUZ 2756</t>
-        </is>
-      </c>
+          <t>6863493329</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-01-1970</t>
+          <t>10-02-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
+          <t>MAXI1002_@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:09</t>
+          <t>02-03-2026 13:46:37</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1711,7 +1731,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 13:22:15</t>
+          <t>02-03-2026 13:47:59</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1719,21 +1739,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 13:20:14</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1741,7 +1753,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26030522792910002676</t>
+          <t>26030522793590002677</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1753,7 +1765,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1765,12 +1777,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>347559</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>89724</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1780,17 +1792,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>REY ALEXANDER</t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1800,43 +1812,47 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6151097298</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6862120974</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AV. RIO SANTA CRUZ 2756</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06-01-2006</t>
+          <t>04-01-1970</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>REYALEXSAN06@GMAIL.COM</t>
+          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:06:58</t>
+          <t>02-03-2026 13:15:09</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1846,7 +1862,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:48</t>
+          <t>02-03-2026 13:22:15</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1854,13 +1870,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-03-2026 13:20:14</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1868,7 +1892,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26030522815370002723</t>
+          <t>26030522792910002676</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1880,7 +1904,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1892,12 +1916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>331568</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1907,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LUIS ROBERTO</t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t xml:space="preserve">CALDERON </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>PASOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1927,10 +1951,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6151040574</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6861194706</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1938,32 +1966,32 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-11-2006</t>
+          <t>06-09-1979</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+          <t>VCALDERON@NORTECHWATER.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:11</t>
+          <t>02-01-2026 14:59:23</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1973,7 +2001,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:49</t>
+          <t>02-03-2026 18:05:18</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1981,13 +2009,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:04:29</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1995,10 +2031,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26030522815780002725</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26020522810100001487</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2007,24 +2047,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347935</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>90025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2034,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRITIAN ALEXIS</t>
+          <t>REY ALEXANDER</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2054,14 +2094,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861367828</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AV. RIO TEPEYAC</t>
-        </is>
-      </c>
+          <t>6151097298</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2069,32 +2105,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-09-1998</t>
+          <t>06-01-2006</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HERLO.ALEXIS@GMAIL.COM</t>
+          <t>REYALEXSAN06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 05:49:56</t>
+          <t>02-03-2026 19:06:58</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2104,29 +2140,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 05:57:29</t>
+          <t>02-03-2026 19:09:48</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-03-2026 05:56:20</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2134,7 +2162,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26030522823980002754</t>
+          <t>26030522815370002723</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2146,24 +2174,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348248</t>
+          <t>347863</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>90028</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2173,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SERGIO ALFREDO</t>
+          <t>LUIS ROBERTO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MONARREZ</t>
+          <t>DE LA FUENTE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2193,7 +2221,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6862116838</t>
+          <t>6151040574</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2204,17 +2232,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21-04-1987</t>
+          <t>14-11-2006</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SMONARREZ@PROTONMAIL.COM</t>
+          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 18:54:51</t>
+          <t>02-03-2026 19:12:11</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2239,18 +2267,18 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 18:57:27</t>
+          <t>02-03-2026 19:14:49</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2261,7 +2289,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26030522856880002815</t>
+          <t>26030522815780002725</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2273,12 +2301,1211 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347935</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90100</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRITIAN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6861367828</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AV. RIO TEPEYAC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>12-09-1998</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>HERLO.ALEXIS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:49:56</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:57:29</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:56:20</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26030522823980002754</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348651</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90816</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRECIA </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OZUNA </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARAGON </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6864195826</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARTA GINECES </t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04-10-1986</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ALINEOA11@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:23:37</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:46:00</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:45:17</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26030522913030002910</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348746</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90911</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NELLY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6862673703</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>03-02-2007</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NELLYCV.05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:30:42</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:32:38</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26030522921270002922</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348041</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90206</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6863457525</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>23-06-2007</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MMICHELL650@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:23:58</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:26:28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26030522839830002778</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348248</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90413</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SERGIO ALFREDO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MONARREZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AGUIRRE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6862116838</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>21-04-1987</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>SMONARREZ@PROTONMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:54:51</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:57:27</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26030522856880002815</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90525</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRADILLA </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SONQUI </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6863413808</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO BALUARTE </t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>13-11-1990</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ALEJANDRA.GS@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:55:50</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:03:34</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:02:58</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26030522876760002846</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>347592</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>89757</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAYARA </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GAMEZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6863949303</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>03-02-1996</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>DAYARA.GAMEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:30:37</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>02-03-2026 14:32:26</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26030522795050002683</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348313</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90478</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA GABRIELA </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENITEZ </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANGUY </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6862135475</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RIO BALUARTE 2211</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>17-08-1986</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>GBMANGUY@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:14:54</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:21:16</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:19:57</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26030522864530002837</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>347962</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90127</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SANDRA LUCIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PARRA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GUEVARA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6864219527</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>12-03-1991</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>LICSANDRAPARRA1027@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:15:40</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:17:17</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26030522875530002845</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>187200</t>
+          <t>331568</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BRAULIO</t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t xml:space="preserve">CALDERON </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>PASOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863669528</t>
+          <t>6861194706</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ASCD</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16-11-2005</t>
+          <t>06-09-1979</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
+          <t>VCALDERON@NORTECHWATER.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27-07-2023 11:07:51</t>
+          <t>02-01-2026 14:59:23</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:48</t>
+          <t>02-03-2026 18:05:18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:17</t>
+          <t>02-03-2026 18:04:29</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,10 +693,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26010522862050005600</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26020522810100001487</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -717,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>187165</t>
+          <t>310968</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84672</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AXEL NOE</t>
+          <t>ESTHER JANETH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RENDON</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VILCHIS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,28 +756,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6531608871</t>
+          <t>6861719313</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-07-2012</t>
+          <t>25-07-1995</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AXEL2011ZV7@GMAIL.COM</t>
+          <t>JANETHMACHADOV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27-07-2023 08:16:44</t>
+          <t>25-08-2025 13:52:20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -798,18 +802,18 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:55</t>
+          <t>03-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -820,10 +824,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522859090002821</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26030522852630002805</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -832,7 +840,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -844,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347516</t>
+          <t>187165</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>84672</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>AXEL NOE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RENDON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LARIOS</t>
+          <t>VILCHIS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,7 +887,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6864601573</t>
+          <t>6531608871</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -890,17 +898,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10-09-2004</t>
+          <t>12-07-2012</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CHRISTIAN.MARTINEZ@CETYS.EDU.MX</t>
+          <t>AXEL2011ZV7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:48:53</t>
+          <t>27-07-2023 08:16:44</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -925,18 +933,18 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 12:57:38</t>
+          <t>03-03-2026 19:31:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -947,14 +955,10 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522881000002857</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522859090002821</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -963,7 +967,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -975,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347521</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89686</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YITZEL ARACELY</t>
+          <t>BRAULIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VILLARRAL</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,43 +1014,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6862765502</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6863669528</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>27-04-2001</t>
+          <t>16-11-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>YITZELVILLAREAL0@GMAIL.COM</t>
+          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:02:09</t>
+          <t>27-07-2023 11:07:51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1056,21 +1064,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 12:59:21</t>
+          <t>03-03-2026 21:18:48</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:17</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1078,14 +1094,10 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26030522881050002858</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26010522862050005600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1094,24 +1106,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347467</t>
+          <t>294579</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89632</t>
+          <t>92077</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARÍA MONSERRAT</t>
+          <t xml:space="preserve">MARCO ANTONIO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t xml:space="preserve">ROCHIN </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,32 +1153,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863453919</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PASEOL DEL SOL</t>
-        </is>
-      </c>
+          <t>6862406745</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05-08-1999</t>
+          <t>28-09-1989</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MONSERRAT.AYALA@UABC.EDU.MX</t>
+          <t>MARCO_ZAZUETA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 09:42:10</t>
+          <t>24-05-2025 07:23:08</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1176,44 +1184,36 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 17:20:31</t>
+          <t>07-03-2026 07:00:32</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:19:44</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,40 +1221,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522890160002869</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522968820002987</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>310968</t>
+          <t>347573</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>89738</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESTHER JANETH</t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,28 +1280,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6861719313</t>
+          <t>6863493329</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-07-1995</t>
+          <t>10-02-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JANETHMACHADOV@GMAIL.COM</t>
+          <t>MAXI1002_@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25-08-2025 13:52:20</t>
+          <t>02-03-2026 13:46:37</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1330,18 +1326,18 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 17:55:45</t>
+          <t>02-03-2026 13:47:59</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1352,14 +1348,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030522852630002805</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522793590002677</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1368,24 +1360,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347417</t>
+          <t>347467</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>89632</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>MARÍA MONSERRAT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,28 +1407,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6601593137</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6863453919</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PASEOL DEL SOL</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10-08-1961</t>
+          <t>05-08-1999</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NEGROSOMEX@ICLOUD.COM</t>
+          <t>MONSERRAT.AYALA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 07:20:27</t>
+          <t>02-03-2026 09:42:10</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1446,36 +1442,44 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 07:23:24</t>
+          <t>04-03-2026 17:20:31</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:19:44</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1483,19 +1487,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26030522782180002649</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26030522890160002869</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1507,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347538</t>
+          <t>347417</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89703</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1522,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MINERVA YISSEL</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1542,32 +1550,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6865448260</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PASEOS DEL SOL</t>
-        </is>
-      </c>
+          <t>6601593137</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28-12-2001</t>
+          <t>10-08-1961</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YISSEL.LOPEZO@GMAIL.COM</t>
+          <t>NEGROSOMEX@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 12:33:14</t>
+          <t>02-03-2026 07:20:27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1577,44 +1581,36 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 17:15:17</t>
+          <t>02-03-2026 07:23:24</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:14:20</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1622,23 +1618,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26030522889750002868</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522782180002649</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1650,12 +1642,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347573</t>
+          <t>347592</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>89757</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1657,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t xml:space="preserve">DAYARA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GAMEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,28 +1677,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863493329</t>
+          <t>6863949303</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10-02-1998</t>
+          <t>03-02-1996</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MAXI1002_@OUTLOOK.ES</t>
+          <t>DAYARA.GAMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 13:46:37</t>
+          <t>02-03-2026 14:30:37</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1731,18 +1723,18 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 13:47:59</t>
+          <t>02-03-2026 14:32:26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1753,7 +1745,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26030522793590002677</t>
+          <t>26030522795050002683</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1765,7 +1757,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1867,7 +1859,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1916,12 +1908,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>331568</t>
+          <t>347538</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1931,17 +1923,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR </t>
+          <t>MINERVA YISSEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALDERON </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PASOS</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1951,67 +1943,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6861194706</t>
+          <t>6865448260</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>PASEOS DEL SOL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06-09-1979</t>
+          <t>28-12-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>VCALDERON@NORTECHWATER.COM</t>
+          <t>YISSEL.LOPEZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-01-2026 14:59:23</t>
+          <t>02-03-2026 12:33:14</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:18</t>
+          <t>04-03-2026 17:15:17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:29</t>
+          <t>04-03-2026 17:14:20</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2031,40 +2023,40 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522810100001487</t>
+          <t>26030522889750002868</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>347962</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>REY ALEXANDER</t>
+          <t>SANDRA LUCIA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,28 +2086,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6151097298</t>
+          <t>6864219527</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>06-01-2006</t>
+          <t>12-03-1991</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>REYALEXSAN06@GMAIL.COM</t>
+          <t>LICSANDRAPARRA1027@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 19:06:58</t>
+          <t>03-03-2026 08:15:40</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2140,12 +2132,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:48</t>
+          <t>04-03-2026 08:17:17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2162,10 +2154,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26030522815370002723</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26030522875530002845</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2174,7 +2170,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2186,12 +2182,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>348041</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>90206</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2201,17 +2197,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LUIS ROBERTO</t>
+          <t xml:space="preserve">MARIANA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,28 +2217,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6151040574</t>
+          <t>6863457525</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14-11-2006</t>
+          <t>23-06-2007</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+          <t>MMICHELL650@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:11</t>
+          <t>03-03-2026 13:23:58</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2267,7 +2263,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:49</t>
+          <t>03-03-2026 13:26:28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2278,7 +2274,7 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26030522815780002725</t>
+          <t>26030522839830002778</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2301,7 +2297,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2313,12 +2309,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347935</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>90025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRITIAN ALEXIS</t>
+          <t>REY ALEXANDER</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,14 +2344,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6861367828</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AV. RIO TEPEYAC</t>
-        </is>
-      </c>
+          <t>6151097298</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2363,32 +2355,32 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-09-1998</t>
+          <t>06-01-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>HERLO.ALEXIS@GMAIL.COM</t>
+          <t>REYALEXSAN06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:49:56</t>
+          <t>02-03-2026 19:06:58</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2398,29 +2390,21 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:57:29</t>
+          <t>02-03-2026 19:09:48</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-03-2026 05:56:20</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2428,7 +2412,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26030522823980002754</t>
+          <t>26030522815370002723</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2440,24 +2424,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348651</t>
+          <t>347863</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90816</t>
+          <t>90028</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2467,17 +2451,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRECIA </t>
+          <t>LUIS ROBERTO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZUNA </t>
+          <t>DE LA FUENTE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARAGON </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2487,79 +2471,67 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6864195826</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CARTA GINECES </t>
-        </is>
-      </c>
+          <t>6151040574</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>04-10-1986</t>
+          <t>14-11-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ALINEOA11@GMAIL.COM</t>
+          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-03-2026 10:23:37</t>
+          <t>02-03-2026 19:12:11</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05-03-2026 10:46:00</t>
+          <t>02-03-2026 19:14:49</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>05-03-2026 10:45:17</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2567,23 +2539,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26030522913030002910</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030522815780002725</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2595,12 +2563,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348746</t>
+          <t>347935</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>90100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2610,17 +2578,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NELLY</t>
+          <t>CRITIAN ALEXIS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2630,43 +2598,47 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862673703</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6861367828</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AV. RIO TEPEYAC</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>03-02-2007</t>
+          <t>12-09-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NELLYCV.05@GMAIL.COM</t>
+          <t>HERLO.ALEXIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-03-2026 16:30:42</t>
+          <t>03-03-2026 05:49:56</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2676,21 +2648,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 16:32:38</t>
+          <t>03-03-2026 05:57:29</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:56:20</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2698,7 +2678,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26030522921270002922</t>
+          <t>26030522823980002754</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2722,12 +2702,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348041</t>
+          <t>347516</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2737,17 +2717,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANA </t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LARIOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2757,28 +2737,28 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6863457525</t>
+          <t>6864601573</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23-06-2007</t>
+          <t>10-09-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MMICHELL650@GMAIL.COM</t>
+          <t>CHRISTIAN.MARTINEZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 13:23:58</t>
+          <t>02-03-2026 11:48:53</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2803,7 +2783,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 13:26:28</t>
+          <t>04-03-2026 12:57:38</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2814,7 +2794,7 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2825,10 +2805,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26030522839830002778</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26030522881000002857</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2849,12 +2833,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348248</t>
+          <t>347521</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2864,17 +2848,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SERGIO ALFREDO</t>
+          <t>YITZEL ARACELY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MONARREZ</t>
+          <t>VILLARRAL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2884,28 +2868,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862116838</t>
+          <t>6862765502</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21-04-1987</t>
+          <t>27-04-2001</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SMONARREZ@PROTONMAIL.COM</t>
+          <t>YITZELVILLAREAL0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:54:51</t>
+          <t>02-03-2026 12:02:09</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2930,7 +2914,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:57:27</t>
+          <t>04-03-2026 12:59:21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2941,7 +2925,7 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2952,10 +2936,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26030522856880002815</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26030522881050002858</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2964,7 +2952,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2976,12 +2964,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348360</t>
+          <t>348313</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90525</t>
+          <t>90478</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2991,17 +2979,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t xml:space="preserve">ANA GABRIELA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRADILLA </t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONQUI </t>
+          <t xml:space="preserve">MANGUY </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3011,12 +2999,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6863413808</t>
+          <t>6862135475</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIO BALUARTE </t>
+          <t>RIO BALUARTE 2211</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3026,52 +3014,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-11-1990</t>
+          <t>17-08-1986</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ALEJANDRA.GS@LIVE.COM.MX</t>
+          <t>GBMANGUY@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-03-2026 08:55:50</t>
+          <t>04-03-2026 05:14:54</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-03-2026 09:03:34</t>
+          <t>04-03-2026 05:21:16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>04-03-2026 09:02:58</t>
+          <t>04-03-2026 05:19:57</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3091,36 +3079,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26030522876760002846</t>
+          <t>26030522864530002837</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347592</t>
+          <t>348360</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89757</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3130,17 +3118,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAYARA </t>
+          <t xml:space="preserve">ALEJANDRA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GAMEZ</t>
+          <t xml:space="preserve">GRADILLA </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t xml:space="preserve">SONQUI </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3150,10 +3138,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6863949303</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6863413808</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO BALUARTE </t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3161,32 +3153,32 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03-02-1996</t>
+          <t>13-11-1990</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>DAYARA.GAMEZ@GMAIL.COM</t>
+          <t>ALEJANDRA.GS@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 14:30:37</t>
+          <t>04-03-2026 08:55:50</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3196,21 +3188,29 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 14:32:26</t>
+          <t>04-03-2026 09:03:34</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:02:58</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26030522795050002683</t>
+          <t>26030522876760002846</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348313</t>
+          <t>348248</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90478</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA GABRIELA </t>
+          <t>SERGIO ALFREDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENITEZ </t>
+          <t>MONARREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANGUY </t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3277,79 +3277,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6862135475</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>RIO BALUARTE 2211</t>
-        </is>
-      </c>
+          <t>6862116838</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>17-08-1986</t>
+          <t>21-04-1987</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>GBMANGUY@HOTMAIL.COM</t>
+          <t>SMONARREZ@PROTONMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-03-2026 05:14:54</t>
+          <t>03-03-2026 18:54:51</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-03-2026 05:21:16</t>
+          <t>03-03-2026 18:57:27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>04-03-2026 05:19:57</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3357,36 +3345,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26030522864530002837</t>
+          <t>26030522856880002815</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347962</t>
+          <t>349151</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90127</t>
+          <t>91316</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3396,17 +3384,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANDRA LUCIA</t>
+          <t>ISBEL SUGEY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>VILLASEÑOR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3416,10 +3404,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6864219527</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6865358043</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PASEOS DEL SOL</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3427,32 +3419,32 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-03-1991</t>
+          <t>26-08-2004</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LICSANDRAPARRA1027@GMAIL.COM</t>
+          <t>SUGEYARCE8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 08:15:40</t>
+          <t>07-03-2026 12:39:30</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3462,21 +3454,29 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-03-2026 08:17:17</t>
+          <t>07-03-2026 12:43:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:42:44</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3484,14 +3484,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26030522875530002845</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030522975110003000</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3500,12 +3496,421 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348651</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90816</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRECIA </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OZUNA </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARAGON </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6864195826</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARTA GINECES </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>04-10-1986</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ALINEOA11@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:23:37</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:46:00</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:45:17</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26030522913030002910</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348746</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90911</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NELLY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6862673703</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>03-02-2007</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NELLYCV.05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:30:42</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:32:38</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26030522921270002922</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348898</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>91063</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ROSARIO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CRISANTO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6861404100</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>06-03-1990</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ROSARIOCRISANTO809@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>06-03-2026 13:08:09</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:44:35</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:39:25</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26170522954770003520</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TEC MXL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>331568</t>
+          <t>147933</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR </t>
+          <t>IMELDA GUADALUPE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALDERON </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PASOS</t>
+          <t>IRIBE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6861194706</t>
+          <t>6863943905</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>EIO AMECA 2006</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>06-09-1979</t>
+          <t>28-11-1980</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>VCALDERON@NORTECHWATER.COM</t>
+          <t>MEDINAIMELDA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-01-2026 14:59:23</t>
+          <t>25-01-2023 20:21:47</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:18</t>
+          <t>14-03-2026 12:54:29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>13-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:29</t>
+          <t>14-03-2026 12:54:04</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,14 +693,10 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26020522810100001487</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030523183710003373</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -709,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>310968</t>
+          <t>305919</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ESTHER JANETH</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MACHADO</t>
+          <t>CAMPAÑA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,28 +752,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6861719313</t>
+          <t>6865702829</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-07-1995</t>
+          <t>23-11-2007</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>JANETHMACHADOV@GMAIL.COM</t>
+          <t>campesinowest@gmail.com</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-08-2025 13:52:20</t>
+          <t>25-07-2025 14:08:19</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 17:55:45</t>
+          <t>09-03-2026 13:27:09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -824,14 +820,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522852630002805</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030523007510003025</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -840,7 +832,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -852,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>187165</t>
+          <t>330389</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84672</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,87 +859,99 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AXEL NOE</t>
+          <t xml:space="preserve">LYDIA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RENDON</t>
+          <t>MUÑIZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VILCHIS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531608871</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>4422028910</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AV. COLORIN 43</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-07-2012</t>
+          <t>15-07-1990</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AXEL2011ZV7@GMAIL.COM</t>
+          <t>LYDIASMUNIZ@YAHOO.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-07-2023 08:16:44</t>
+          <t>26-12-2025 13:13:52</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:55</t>
+          <t>18-03-2026 10:40:11</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>18-03-2026 10:39:35</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,19 +959,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522859090002821</t>
+          <t>26030523288340003560</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -979,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>187200</t>
+          <t>328280</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BRAULIO</t>
+          <t>ABDIEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863669528</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ASCD</t>
-        </is>
-      </c>
+          <t>6863551724</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1029,32 +1029,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16-11-2005</t>
+          <t>19-01-2002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
+          <t>BEBIS1901@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27-07-2023 11:07:51</t>
+          <t>09-12-2025 21:18:58</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1064,29 +1064,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:48</t>
+          <t>10-03-2026 16:48:39</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03-03-2026 21:18:17</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,10 +1086,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26010522862050005600</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26030523058070003139</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1106,24 +1102,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>294579</t>
+          <t>116291</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCO ANTONIO </t>
+          <t>CARLOS RUBEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>FIGUEROA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHIN </t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,10 +1149,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6862406745</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6861503305</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LOS ANGELES 2168</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1164,22 +1164,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-09-1989</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MARCO_ZAZUETA@YAHOO.COM</t>
+          <t>CARLOSFIGUEROA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>24-05-2025 07:23:08</t>
+          <t>15-08-2022 21:54:11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1189,28 +1189,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>07-03-2026 07:00:32</t>
+          <t>09-03-2026 19:36:27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1221,36 +1221,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522968820002987</t>
+          <t>26010523028210006102</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347573</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>BRAULIO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,10 +1280,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6863493329</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6863669528</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1291,32 +1295,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10-02-1998</t>
+          <t>16-11-2005</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MAXI1002_@OUTLOOK.ES</t>
+          <t>BRAULIOSILVAHARO161100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:46:37</t>
+          <t>27-07-2023 11:07:51</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1326,21 +1330,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:47:59</t>
+          <t>03-03-2026 21:18:48</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:17</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1348,7 +1360,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030522793590002677</t>
+          <t>26010522862050005600</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1360,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347467</t>
+          <t>294579</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89632</t>
+          <t>92077</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARÍA MONSERRAT</t>
+          <t xml:space="preserve">MARCO ANTONIO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t xml:space="preserve">ROCHIN </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,32 +1419,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863453919</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PASEOL DEL SOL</t>
-        </is>
-      </c>
+          <t>6862406745</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05-08-1999</t>
+          <t>28-09-1989</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MONSERRAT.AYALA@UABC.EDU.MX</t>
+          <t>MARCO_ZAZUETA@YAHOO.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 09:42:10</t>
+          <t>24-05-2025 07:23:08</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1442,44 +1450,36 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 17:20:31</t>
+          <t>07-03-2026 07:00:32</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:19:44</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1487,23 +1487,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26030522890160002869</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522968820002987</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1515,12 +1511,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347417</t>
+          <t>161243</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89582</t>
+          <t>58776</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1526,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>JAZMINE NAVIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOLIS </t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,28 +1546,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6601593137</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6862300447</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10-08-1961</t>
+          <t>22-08-1987</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NEGROSOMEX@ICLOUD.COM</t>
+          <t>NAVILAPARICIO-@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 07:20:27</t>
+          <t>29-03-2023 08:42:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1581,36 +1581,44 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 07:23:24</t>
+          <t>19-03-2026 08:26:38</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>19-03-2026 08:25:55</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1618,36 +1626,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26030522782180002649</t>
+          <t>26010523322810007082</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347592</t>
+          <t>187165</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89757</t>
+          <t>84672</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1657,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAYARA </t>
+          <t>AXEL NOE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GAMEZ</t>
+          <t>RENDON</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>VILCHIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1677,28 +1685,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863949303</t>
+          <t>6531608871</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-02-1996</t>
+          <t>12-07-2012</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DAYARA.GAMEZ@GMAIL.COM</t>
+          <t>AXEL2011ZV7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 14:30:37</t>
+          <t>27-07-2023 08:16:44</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1723,18 +1731,18 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 14:32:26</t>
+          <t>03-03-2026 19:31:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1745,7 +1753,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26030522795050002683</t>
+          <t>26030522859090002821</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1757,7 +1765,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1769,12 +1777,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347559</t>
+          <t>205687</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1784,17 +1792,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ROSA MARIA</t>
+          <t>EVELIN AYLIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>OYARZABAL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t xml:space="preserve">ALTERETE </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1804,12 +1812,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862120974</t>
+          <t>6865050526</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AV. RIO SANTA CRUZ 2756</t>
+          <t>GONZALEZ ORTEGA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1819,52 +1827,52 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-01-1970</t>
+          <t>05-11-2003</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
+          <t>EXCLUBPTRABAJO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:09</t>
+          <t>07-11-2023 18:54:40</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 13:22:15</t>
+          <t>19-03-2026 21:10:50</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 13:20:14</t>
+          <t>19-03-2026 21:07:22</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1884,36 +1892,36 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26030522792910002676</t>
+          <t>26030523345440003678</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347538</t>
+          <t>113671</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89703</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1923,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MINERVA YISSEL</t>
+          <t>TLALLI ZACNITE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1943,12 +1951,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6865448260</t>
+          <t>6862408635</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PASEOS DEL SOL</t>
+          <t xml:space="preserve">MEZQUITAL 2201 </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1958,17 +1966,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28-12-2001</t>
+          <t>25-07-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>YISSEL.LOPEZO@GMAIL.COM</t>
+          <t>TLALLI.MORENO@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 12:33:14</t>
+          <t>04-08-2022 14:09:27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1978,32 +1986,32 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:15:17</t>
+          <t>18-03-2026 14:39:44</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:14:20</t>
+          <t>18-03-2026 14:37:52</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2013,7 +2021,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2023,23 +2031,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26030522889750002868</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030523293260003579</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Eduardo Arellano Varela</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2051,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347962</t>
+          <t>125853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90127</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2070,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANDRA LUCIA</t>
+          <t>MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>CINCO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>QUEZADA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,33 +2090,37 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6864219527</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6864206155</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MONTEZUMA SUR 3443</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-03-1991</t>
+          <t>12-05-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>LICSANDRAPARRA1027@GMAIL.COM</t>
+          <t>KLAPIACINCO@UABC.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:15:40</t>
+          <t>27-09-2022 08:26:33</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2122,22 +2130,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 08:17:17</t>
+          <t>17-03-2026 08:31:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2154,23 +2162,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26030522875530002845</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26010523246880006828</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Cristobal Lopez Miranda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2182,12 +2186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348041</t>
+          <t>243567</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANA </t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ORNELAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,67 +2221,79 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863457525</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6864055261</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-06-2007</t>
+          <t>11-09-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MMICHELL650@GMAIL.COM</t>
+          <t>ORNELASMARCOICV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:23:58</t>
+          <t>02-07-2024 18:40:11</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:26:28</t>
+          <t>19-03-2026 20:15:29</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:14:24</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2285,36 +2301,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26030522839830002778</t>
+          <t>26160523343530003844</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>310968</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>REY ALEXANDER</t>
+          <t>ESTHER JANETH</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MACHADO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,28 +2360,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6151097298</t>
+          <t>6861719313</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-01-2006</t>
+          <t>25-07-1995</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>REYALEXSAN06@GMAIL.COM</t>
+          <t>JANETHMACHADOV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:06:58</t>
+          <t>25-08-2025 13:52:20</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2390,12 +2406,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:09:48</t>
+          <t>03-03-2026 17:55:45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2412,10 +2428,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26030522815370002723</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26030522852630002805</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2436,12 +2456,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>346523</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>88688</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2451,17 +2471,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LUIS ROBERTO</t>
+          <t>YAZMIN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DE LA FUENTE</t>
+          <t>SALDAÑA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2471,43 +2491,47 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6151040574</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6861918143</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RIO COATZACOALCOS</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14-11-2006</t>
+          <t>05-05-1989</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+          <t>YAZMIN.SAL89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:12:11</t>
+          <t>25-02-2026 16:19:50</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2517,21 +2541,29 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:14:49</t>
+          <t>14-03-2026 12:47:31</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:46:58</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2539,10 +2571,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26030522815780002725</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26030523183570003371</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2551,7 +2587,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Alberto  Esquivias Robles</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2563,12 +2599,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347935</t>
+          <t>331568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,17 +2614,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRITIAN ALEXIS</t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">CALDERON </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PASOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2598,12 +2634,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861367828</t>
+          <t>6861194706</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AV. RIO TEPEYAC</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2613,17 +2649,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12-09-1998</t>
+          <t>06-09-1979</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>HERLO.ALEXIS@GMAIL.COM</t>
+          <t>VCALDERON@NORTECHWATER.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 05:49:56</t>
+          <t>02-01-2026 14:59:23</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2648,17 +2684,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 05:57:29</t>
+          <t>02-03-2026 18:05:18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-03-2026 05:56:20</t>
+          <t>02-03-2026 18:04:29</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2678,10 +2714,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26030522823980002754</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26020522810100001487</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2690,24 +2730,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347516</t>
+          <t>344694</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2717,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>CRISTIAN GABRIELA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>AHUMADA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LARIOS</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2737,7 +2777,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6864601573</t>
+          <t>6861316485</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2748,17 +2788,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-09-2004</t>
+          <t>20-06-2007</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CHRISTIAN.MARTINEZ@CETYS.EDU.MX</t>
+          <t>GABRIELA.AHUMADA2007@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 11:48:53</t>
+          <t>17-02-2026 20:01:21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2783,12 +2823,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-03-2026 12:57:38</t>
+          <t>09-03-2026 21:28:47</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2805,7 +2845,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26030522881000002857</t>
+          <t>26020523033850001825</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2821,7 +2861,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2833,12 +2873,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347521</t>
+          <t>347417</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89686</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2848,17 +2888,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>YITZEL ARACELY</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VILLARRAL</t>
+          <t xml:space="preserve">SOLIS </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2868,33 +2908,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862765502</t>
+          <t>6601593137</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>27-04-2001</t>
+          <t>10-08-1961</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>YITZELVILLAREAL0@GMAIL.COM</t>
+          <t>NEGROSOMEX@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 12:02:09</t>
+          <t>02-03-2026 07:20:27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2904,28 +2944,28 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-03-2026 12:59:21</t>
+          <t>02-03-2026 07:23:24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2936,23 +2976,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26030522881050002858</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26030522782180002649</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2964,12 +3000,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348313</t>
+          <t>347592</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90478</t>
+          <t>89757</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2979,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA GABRIELA </t>
+          <t xml:space="preserve">DAYARA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENITEZ </t>
+          <t>GAMEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANGUY </t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2999,14 +3035,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6862135475</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>RIO BALUARTE 2211</t>
-        </is>
-      </c>
+          <t>6863949303</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3014,64 +3046,56 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17-08-1986</t>
+          <t>03-02-1996</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>GBMANGUY@HOTMAIL.COM</t>
+          <t>DAYARA.GAMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-03-2026 05:14:54</t>
+          <t>02-03-2026 14:30:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-03-2026 05:21:16</t>
+          <t>02-03-2026 14:32:26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>04-03-2026 05:19:57</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3079,36 +3103,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26030522864530002837</t>
+          <t>26030522795050002683</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Alberto  Esquivias Robles</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348360</t>
+          <t>347467</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90525</t>
+          <t>89632</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3118,17 +3142,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t>MARÍA MONSERRAT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRADILLA </t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONQUI </t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3138,12 +3162,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6863413808</t>
+          <t>6863453919</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIO BALUARTE </t>
+          <t>PASEOL DEL SOL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3153,42 +3177,42 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-11-1990</t>
+          <t>05-08-1999</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ALEJANDRA.GS@LIVE.COM.MX</t>
+          <t>MONSERRAT.AYALA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-03-2026 08:55:50</t>
+          <t>02-03-2026 09:42:10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 09:03:34</t>
+          <t>04-03-2026 17:20:31</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3198,7 +3222,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-03-2026 09:02:58</t>
+          <t>04-03-2026 17:19:44</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3218,19 +3242,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26030522876760002846</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26030522890160002869</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Juan Eduardo Arellano Varela</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3242,12 +3270,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348248</t>
+          <t>347538</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90413</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3257,17 +3285,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SERGIO ALFREDO</t>
+          <t>MINERVA YISSEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MONARREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3277,67 +3305,79 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6862116838</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6865448260</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PASEOS DEL SOL</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-04-1987</t>
+          <t>28-12-2001</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SMONARREZ@PROTONMAIL.COM</t>
+          <t>YISSEL.LOPEZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:54:51</t>
+          <t>02-03-2026 12:33:14</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:57:27</t>
+          <t>04-03-2026 17:15:17</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:14:20</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3345,14 +3385,18 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26030522856880002815</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26030522889750002868</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3369,12 +3413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349151</t>
+          <t>347559</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91316</t>
+          <t>89724</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3384,17 +3428,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ISBEL SUGEY</t>
+          <t>ROSA MARIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VILLASEÑOR</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3404,12 +3448,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6865358043</t>
+          <t>6862120974</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PASEOS DEL SOL</t>
+          <t>AV. RIO SANTA CRUZ 2756</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3419,17 +3463,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-08-2004</t>
+          <t>04-01-1970</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SUGEYARCE8@GMAIL.COM</t>
+          <t>R.RODRIGUEZ.A@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>07-03-2026 12:39:30</t>
+          <t>02-03-2026 13:15:09</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3454,17 +3498,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>07-03-2026 12:43:25</t>
+          <t>02-03-2026 13:22:15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>07-03-2026 12:42:44</t>
+          <t>02-03-2026 13:20:14</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3484,7 +3528,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26030522975110003000</t>
+          <t>26030522792910002676</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3508,12 +3552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348651</t>
+          <t>347573</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90816</t>
+          <t>89738</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3523,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRECIA </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZUNA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARAGON </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3543,79 +3587,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6864195826</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CARTA GINECES </t>
-        </is>
-      </c>
+          <t>6863493329</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>04-10-1986</t>
+          <t>10-02-1998</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ALINEOA11@GMAIL.COM</t>
+          <t>MAXI1002_@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-03-2026 10:23:37</t>
+          <t>02-03-2026 13:46:37</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-03-2026 10:46:00</t>
+          <t>02-03-2026 13:47:59</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>05-03-2026 10:45:17</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3623,23 +3655,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26030522913030002910</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26030522793590002677</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3651,12 +3679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348746</t>
+          <t>347962</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3666,17 +3694,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NELLY</t>
+          <t>SANDRA LUCIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3686,7 +3714,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862673703</t>
+          <t>6864219527</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3697,17 +3725,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-02-2007</t>
+          <t>12-03-1991</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>NELLYCV.05@GMAIL.COM</t>
+          <t>LICSANDRAPARRA1027@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>05-03-2026 16:30:42</t>
+          <t>03-03-2026 08:15:40</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3732,12 +3760,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>05-03-2026 16:32:38</t>
+          <t>04-03-2026 08:17:17</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3754,10 +3782,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26030522921270002922</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+          <t>26030522875530002845</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3766,24 +3798,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348898</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>91063</t>
+          <t>90025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3793,17 +3825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROSARIO DEL CARMEN</t>
+          <t>REY ALEXANDER</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CRISANTO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3813,47 +3845,43 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861404100</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6151097298</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>06-01-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ROSARIOCRISANTO809@GMAIL.COM</t>
+          <t>REYALEXSAN06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>06-03-2026 13:08:09</t>
+          <t>02-03-2026 19:06:58</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3863,29 +3891,21 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>06-03-2026 16:44:35</t>
+          <t>02-03-2026 19:09:48</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>06-03-2026 16:39:25</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3893,7 +3913,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522954770003520</t>
+          <t>26030522815370002723</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3905,12 +3925,6135 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>347863</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90028</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LUIS ROBERTO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DE LA FUENTE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MENDEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6151040574</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14-11-2006</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>LUISDELAFUENTE1411@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:12:11</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:14:49</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26030522815780002725</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>347935</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90100</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRISTIAN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6861367828</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AV. RIO TEPEYAC</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>12-09-1998</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HERLO.ALEXIS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:49:56</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:57:29</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:56:20</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26030522823980002754</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347516</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>LARIOS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6864601573</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>10-09-2004</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CHRISTIAN.MARTINEZ@CETYS.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:48:53</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:57:38</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26030522881000002857</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>347521</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>89686</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YITZEL ARACELY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VILLARRAL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CANO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6862765502</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>27-04-2001</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>YITZELVILLAREAL0@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:02:09</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:59:21</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26030522881050002858</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>348244</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>90409</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DULCE NOHEMI</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6871156878</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MONARCAS RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>31-08-2001</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DULCENOHEMISOTOMORENO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:49:04</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:32:38</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:31:43</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26030523064440003151</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>348248</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90413</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SERGIO ALFREDO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MONARREZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AGUIRRE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6862116838</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>21-04-1987</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>SMONARREZ@PROTONMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:54:51</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:57:27</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26030522856880002815</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>348651</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90816</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GRECIA ALINE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSUNA </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARAGON </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6864195826</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARTA GINECES </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>04-10-1986</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ALINEOA11@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:23:37</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:46:00</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>05-03-2026 10:45:17</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26030522913030002910</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348746</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90911</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NELLY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPOS </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6862673703</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>03-02-2007</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NELLYCV.05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:30:42</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:32:38</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26030522921270002922</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>348041</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90206</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANA </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6863457525</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>23-06-2007</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>MMICHELL650@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:23:58</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:26:28</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26030522839830002778</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>348360</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>90525</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRADILLA </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SONQUI </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6863413808</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO BALUARTE </t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>13-11-1990</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ALEJANDRA.GS@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:55:50</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:03:34</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:02:58</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26030522876760002846</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>348898</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>91063</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ROSARIO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CRISANTO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6861404100</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>06-03-1990</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ROSARIOCRISANTO809@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>06-03-2026 13:08:09</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:44:35</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:39:25</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26170522954770003520</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Saul  Galeana</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349116</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91281</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUSANA </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAREDES </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6863148464</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEXICALI </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>11-08-1986</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SL0718482@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>07-03-2026 10:21:41</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:50:11</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:49:48</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26030523183620003372</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349562</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91727</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>KEVIN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BAHENA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>LÓPEZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7351745402</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>29-12-1998</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>KEVIN.BL2912@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:45:57</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:11:17</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26030523130550003284</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>348313</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90478</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA GABRIELA </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENITEZ </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANGUY </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6862135475</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RIO BALUARTE 2211</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>17-08-1986</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>GBMANGUY@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:14:54</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:21:16</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:19:57</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26030522864530002837</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>349311</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>91476</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6861459647</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RIO CHAMPOTON SUR 3273</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25-09-2008</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>VEGADUARTESANTIAGOALEXANDRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:58:38</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:00:00</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>10-03-2026 06:59:09</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26030523042970003099</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>CONSUELO ELOISA OLIVARES SALAS</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>349405</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91570</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROCIO SCARLETT </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAREZ </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAEZ </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6864417723</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>06-12-2012</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ROCIOJUAREZP@EDU.COM.MX</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>09-03-2026 12:43:54</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>09-03-2026 12:46:19</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26030523006360003023</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>349861</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>92026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAOLA </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>JAUREGUI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6862485068</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LOS ENCINOS</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>14-11-1995</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>JRG1795JZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:42:16</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:45:07</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:44:36</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26030523053530003130</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>349890</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>92055</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JATZIRY PAOLA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>LUQUEN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6861544316</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>25-12-2007</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>PAOLPZZE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:37:37</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>12-03-2026 16:23:47</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26030523126200003272</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>349151</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>91316</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ISBEL SUGEY</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>VILLASEÑOR</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ARCE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6865358043</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PASEOS DEL SOL</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>26-08-2004</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>SUGEYARCE8@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:39:30</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:43:25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:42:44</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26030522975110003000</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>349295</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>91460</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KARLA LOURDES</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6863153221</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>CERRADA MISION SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>18-01-1998</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>YOELGARCIA2216@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:50:03</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:20:48</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:20:16</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26030522998850003008</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>349298</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>91463</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GEMA LETICIA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6861855021</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>REY SOL 1785</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>08-08-1991</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>GEMITHA263@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:57:17</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:15:23</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:15:01</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26030522998740003007</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>349858</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>92023</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>YURIRIA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6864201046</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EL ROBLEDO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>11-09-1984</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>YURIRIAGONZALEZFLORES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:31:26</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:35:18</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:34:40</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26030523053330003128</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>349886</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>92051</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BRANDON</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LEAL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ROSAS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6861927001</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>16-07-2004</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LEALROSAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:27:05</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:28:15</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26030523057110003134</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>349533</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>91698</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENESIS FERNANDA </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6863407812</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SANTO NIÑO</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>15-09-1996</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>GENESISMTZ921@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:12:16</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:17:48</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:15:07</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26030523016940003047</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>349852</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>92017</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GRISELDA CRISTINA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORZAGARAY </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6861890677</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>VALLE DEL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>02-12-1984</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NINI211322@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:24:50</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:28:48</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:27:23</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26030523053090003127</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>350480</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>92644</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JHOSELIN ARACELI</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LLAMAS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SÁNCHEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6862809799</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>09-05-2006</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>JHOSELINLLAMAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:48:58</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:54:01</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26030523203600003379</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>349888</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>92053</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EVELYN SUSANA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ULLOA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6862362229</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>09-03-2007</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ZUÑIGAEVELYN517@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:31:18</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:32:32</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26030523057310003135</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>350338</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>92502</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MARTIN JAVIER</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>GAMBOA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6861436865</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NUEVO MEXICALI</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>06-08-1984</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>RODRIGUEZGAMBOAJAVIER2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:13:29</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:37:30</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:36:49</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26030523158990003337</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>351003</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>93167</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARMEN ALICIA </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASCASIO </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6862369898</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO PANUCO </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>01-05-1994</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CARMENALICIA1594@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:46:36</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:50:06</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:49:44</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26030523211030003382</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>351024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>93188</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IAN MAURICIO </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMARGO </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARGUMEDA </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6863577693</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO MIZITLAN </t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>26-11-2000</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CAMARGO.IAN@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:21:16</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:26:28</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:25:57</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26030523212400003384</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>350260</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>92424</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NINUSHKA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GALVEZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6862110902</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PIÑA DEL RIO ESTE 3589</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>27-11-1974</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>RODA_FACTURACION@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>12-03-2026 07:11:33</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>14-03-2026 06:23:52</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>14-03-2026 06:21:14</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26030523176300003361</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>CONSUELO ELOISA OLIVARES SALAS</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>350487</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>92651</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ANA XITLALI</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FIGUEROA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6861107952</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>MICHOACAN DE OCAMPO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>04-06-2005</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>HAX.F05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:29:59</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:32:55</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:31:57</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26030523137190003299</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>350983</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>93147</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>JHARETZY ANDREA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLAMAS </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6864022825</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>28-01-2008</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ARACELISANCHEZZ175@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:57:42</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:58:25</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26030523203670003380</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>349901</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>92066</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MEYLEN ANETH</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>VALDERRABANO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>URBANO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6862393472</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>18-06-2007</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>MEYLEN.URBANO1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:25:51</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:39:03</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26030523099770003214</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Juan Eduardo Arellano Varela</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>350157</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>92322</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SAMUEL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>OROZCO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6862987036</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>29-04-1993</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>SAMUEL11490304@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:49:55</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIO PERSAL 2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>583.33</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>11-03-2026 16:52:05</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>10-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26030523093680003205</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>350484</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>92648</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MARIA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUSTOS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6865706439</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>VILLAS DEL PALMAR</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>28-03-1993</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ANGELACIFER08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:15:11</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:18:20</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:17:31</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26030523136730003298</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>351504</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>93668</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KARLA NEREIDA </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENITEZ </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REYES </t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6861152013</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>RIO AROS</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>16-09-1986</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>KARLADREYES@ULOOCK.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>17-03-2026 13:18:04</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>17-03-2026 13:25:55</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>17-03-2026 13:24:27</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26030523252740003473</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>351603</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>93767</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LILIAN LUCERO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALE </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6861170439</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>21-06-1990</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>LILIANMORALESGRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:45:18</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:46:50</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26030523262910003502</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>351263</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>93427</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ANABEL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>IZQUIERDO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6863073645</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>23-07-1988</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ANABELROJAS800@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:15:57</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:21:10</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:20:39</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26030523228520003418</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>351403</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>93567</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA FERNANDA </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONTES </t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6862416759</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAN RICARDO </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>05-10-1994</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>FERNANDAGARCIAM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>17-03-2026 05:26:02</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>17-03-2026 05:31:33</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>17-03-2026 05:30:57</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26030523237840003447</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>351532</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>93696</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRACIELA MARIA </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AGUIRRE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ESQUER</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6865692134</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>MISION DEL VALLE</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>02-10-1967</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>GRACI_MA@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>17-03-2026 14:56:18</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:17:46</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:16:25</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26030523255770003483</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>351259</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>93423</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ABDALA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PARKER</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6863579472</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>31-01-1988</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ORION117.PARKER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:08:23</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:14:33</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:13:50</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26030523228240003417</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Jesus Alberto  Esquivias Robles</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>351826</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>93990</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HECTOR </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6864401345</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>22-10-2006</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>RDZ.HECTOR2210@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:49:42</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:51:28</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26030523291840003575</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>351469</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>93633</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MARIBEL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DE PIRRONGELLI</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6865783550</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO SANTA MARIA </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>01-01-1971</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>GRUPOMYD@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>17-03-2026 11:41:10</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:09:17</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:08:52</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26030523290730003569</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>351470</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>93634</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ANGEL DANIEL</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PIRRONGELI</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MANRIQUE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6861478843</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>RIO SANTA MARIA 4025</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>01-08-1972</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NEGOCIOASUMEDIDA@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>17-03-2026 11:42:18</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:06:28</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:05:52</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26030523290660003568</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
